--- a/gui/rebalance_localizations.xlsx
+++ b/gui/rebalance_localizations.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">rebalance_localizations!$A$1:$K$1095</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">rebalance_localizations!$A$1:$K$1096</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5263" uniqueCount="4673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5268" uniqueCount="4678">
   <si>
     <t xml:space="preserve">ENGLISH</t>
   </si>
@@ -5338,6 +5338,21 @@
     <t xml:space="preserve">地下水井</t>
   </si>
   <si>
+    <t xml:space="preserve">gui/hud/info_idle_upkeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upkeep when idle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вартість утримання в умовах простою</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unterhaltskosten im Leerlauf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闲置时的维护成本</t>
+  </si>
+  <si>
     <t xml:space="preserve">gui/hud/objective_name/generic/investigate_anomaly</t>
   </si>
   <si>
@@ -14828,7 +14843,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14956,12 +14971,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="7" tint="-0.5"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -15005,7 +15014,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -15067,10 +15076,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -15392,7 +15397,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1095"/>
+  <dimension ref="A1:L1096"/>
   <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="65.45"/>
@@ -21418,21 +21423,21 @@
       <c r="D357" s="4" t="s">
         <v>1669</v>
       </c>
+      <c r="F357" s="6" t="s">
+        <v>1670</v>
+      </c>
+      <c r="I357" s="15" t="s">
+        <v>1671</v>
+      </c>
     </row>
     <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>1672</v>
-      </c>
-      <c r="F358" s="6" t="s">
-        <v>1673</v>
-      </c>
-      <c r="I358" s="15" t="s">
         <v>1674</v>
       </c>
     </row>
@@ -21559,599 +21564,599 @@
       <c r="A366" s="1" t="s">
         <v>1710</v>
       </c>
-      <c r="B366" s="1" t="s">
+      <c r="B366" s="2" t="s">
         <v>1711</v>
       </c>
+      <c r="D366" s="4" t="s">
+        <v>1712</v>
+      </c>
       <c r="F366" s="6" t="s">
-        <v>1712</v>
+        <v>1713</v>
+      </c>
+      <c r="I366" s="15" t="s">
+        <v>1714</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="F367" s="6" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="F368" s="6" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>1719</v>
-      </c>
-      <c r="B369" s="2" t="s">
-        <v>1720</v>
-      </c>
-      <c r="D369" s="4" t="s">
         <v>1721</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="F369" s="6" t="s">
+        <v>1723</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="D418" s="4" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="D419" s="4" t="s">
-        <v>1871</v>
-      </c>
-      <c r="F419" s="6" t="s">
-        <v>1872</v>
-      </c>
-      <c r="I419" s="15" t="s">
         <v>1873</v>
       </c>
     </row>
@@ -22194,33 +22199,33 @@
         <v>1884</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>1870</v>
+        <v>1885</v>
       </c>
       <c r="D422" s="4" t="s">
-        <v>1871</v>
+        <v>1886</v>
       </c>
       <c r="F422" s="6" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="I422" s="15" t="s">
-        <v>1873</v>
-      </c>
-    </row>
-    <row r="423" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="423" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>1887</v>
+        <v>1875</v>
       </c>
       <c r="D423" s="4" t="s">
-        <v>1888</v>
+        <v>1876</v>
       </c>
       <c r="F423" s="6" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="I423" s="15" t="s">
-        <v>1890</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22274,7 +22279,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="427" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
         <v>1906</v>
       </c>
@@ -22284,43 +22289,43 @@
       <c r="D427" s="4" t="s">
         <v>1908</v>
       </c>
+      <c r="F427" s="6" t="s">
+        <v>1909</v>
+      </c>
+      <c r="I427" s="15" t="s">
+        <v>1910</v>
+      </c>
     </row>
     <row r="428" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>1909</v>
-      </c>
-      <c r="B428" s="1" t="s">
-        <v>1910</v>
+        <v>1911</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>1912</v>
       </c>
       <c r="D428" s="4" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>1912</v>
-      </c>
-      <c r="B429" s="2" t="s">
-        <v>1913</v>
+        <v>1914</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>1915</v>
       </c>
       <c r="D429" s="4" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="D430" s="4" t="s">
-        <v>1917</v>
-      </c>
-      <c r="F430" s="6" t="s">
-        <v>1918</v>
-      </c>
-      <c r="I430" s="15" t="s">
         <v>1919</v>
       </c>
     </row>
@@ -22345,64 +22350,64 @@
       <c r="A432" s="1" t="s">
         <v>1925</v>
       </c>
-      <c r="B432" s="1" t="s">
+      <c r="B432" s="2" t="s">
         <v>1926</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>1927</v>
       </c>
+      <c r="F432" s="6" t="s">
+        <v>1928</v>
+      </c>
+      <c r="I432" s="15" t="s">
+        <v>1929</v>
+      </c>
     </row>
     <row r="433" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>1929</v>
+        <v>1934</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>1930</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="D435" s="4" t="s">
-        <v>1934</v>
-      </c>
-    </row>
-    <row r="436" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="436" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>1935</v>
-      </c>
-      <c r="B436" s="2" t="s">
-        <v>1936</v>
+        <v>1937</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>1938</v>
       </c>
       <c r="D436" s="4" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F436" s="6" t="s">
-        <v>1938</v>
-      </c>
-      <c r="I436" s="7" t="s">
         <v>1939</v>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
         <v>1940</v>
       </c>
@@ -22415,7 +22420,7 @@
       <c r="F437" s="6" t="s">
         <v>1943</v>
       </c>
-      <c r="I437" s="15" t="s">
+      <c r="I437" s="7" t="s">
         <v>1944</v>
       </c>
     </row>
@@ -22526,33 +22531,33 @@
         <v>1975</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>1971</v>
+        <v>1976</v>
       </c>
       <c r="D444" s="4" t="s">
-        <v>1972</v>
+        <v>1977</v>
       </c>
       <c r="F444" s="6" t="s">
-        <v>1973</v>
+        <v>1978</v>
       </c>
       <c r="I444" s="15" t="s">
-        <v>1974</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B445" s="2" t="s">
         <v>1976</v>
       </c>
-      <c r="B445" s="2" t="s">
+      <c r="D445" s="4" t="s">
         <v>1977</v>
       </c>
-      <c r="D445" s="4" t="s">
+      <c r="F445" s="6" t="s">
         <v>1978</v>
       </c>
-      <c r="F445" s="6" t="s">
+      <c r="I445" s="15" t="s">
         <v>1979</v>
-      </c>
-      <c r="I445" s="15" t="s">
-        <v>1980</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22577,33 +22582,33 @@
         <v>1986</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>1982</v>
+        <v>1987</v>
       </c>
       <c r="D447" s="4" t="s">
-        <v>1983</v>
+        <v>1988</v>
       </c>
       <c r="F447" s="6" t="s">
-        <v>1984</v>
+        <v>1989</v>
       </c>
       <c r="I447" s="15" t="s">
-        <v>1985</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B448" s="2" t="s">
         <v>1987</v>
       </c>
-      <c r="B448" s="2" t="s">
+      <c r="D448" s="4" t="s">
         <v>1988</v>
       </c>
-      <c r="D448" s="4" t="s">
+      <c r="F448" s="6" t="s">
         <v>1989</v>
       </c>
-      <c r="F448" s="6" t="s">
+      <c r="I448" s="15" t="s">
         <v>1990</v>
-      </c>
-      <c r="I448" s="15" t="s">
-        <v>1991</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22679,33 +22684,33 @@
         <v>2012</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>2009</v>
+        <v>2014</v>
       </c>
       <c r="F453" s="6" t="s">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="I453" s="15" t="s">
-        <v>2011</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B454" s="2" t="s">
         <v>2013</v>
       </c>
-      <c r="B454" s="2" t="s">
+      <c r="D454" s="4" t="s">
         <v>2014</v>
       </c>
-      <c r="D454" s="4" t="s">
+      <c r="F454" s="6" t="s">
         <v>2015</v>
       </c>
-      <c r="F454" s="6" t="s">
+      <c r="I454" s="15" t="s">
         <v>2016</v>
-      </c>
-      <c r="I454" s="15" t="s">
-        <v>2017</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22764,33 +22769,33 @@
         <v>2033</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="D458" s="4" t="s">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="F458" s="6" t="s">
-        <v>2031</v>
+        <v>2036</v>
       </c>
       <c r="I458" s="15" t="s">
-        <v>2032</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B459" s="2" t="s">
         <v>2034</v>
       </c>
-      <c r="B459" s="2" t="s">
+      <c r="D459" s="4" t="s">
         <v>2035</v>
       </c>
-      <c r="D459" s="4" t="s">
+      <c r="F459" s="6" t="s">
         <v>2036</v>
       </c>
-      <c r="F459" s="6" t="s">
+      <c r="I459" s="15" t="s">
         <v>2037</v>
-      </c>
-      <c r="I459" s="15" t="s">
-        <v>2038</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22798,33 +22803,33 @@
         <v>2039</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1971</v>
+        <v>2040</v>
       </c>
       <c r="D460" s="4" t="s">
-        <v>1972</v>
+        <v>2041</v>
       </c>
       <c r="F460" s="6" t="s">
-        <v>1973</v>
+        <v>2042</v>
       </c>
       <c r="I460" s="15" t="s">
-        <v>1974</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>2040</v>
+        <v>2044</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>2041</v>
+        <v>1976</v>
       </c>
       <c r="D461" s="4" t="s">
-        <v>2042</v>
+        <v>1977</v>
       </c>
       <c r="F461" s="6" t="s">
-        <v>2043</v>
+        <v>1978</v>
       </c>
       <c r="I461" s="15" t="s">
-        <v>2044</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="462" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22849,33 +22854,33 @@
         <v>2050</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>2046</v>
+        <v>2051</v>
       </c>
       <c r="D463" s="4" t="s">
-        <v>2047</v>
+        <v>2052</v>
       </c>
       <c r="F463" s="6" t="s">
-        <v>2048</v>
+        <v>2053</v>
       </c>
       <c r="I463" s="15" t="s">
-        <v>2049</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B464" s="2" t="s">
         <v>2051</v>
       </c>
-      <c r="B464" s="2" t="s">
+      <c r="D464" s="4" t="s">
         <v>2052</v>
       </c>
-      <c r="D464" s="4" t="s">
+      <c r="F464" s="6" t="s">
         <v>2053</v>
       </c>
-      <c r="F464" s="6" t="s">
+      <c r="I464" s="15" t="s">
         <v>2054</v>
-      </c>
-      <c r="I464" s="15" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="465" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22934,33 +22939,33 @@
         <v>2071</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>2067</v>
+        <v>2072</v>
       </c>
       <c r="D468" s="4" t="s">
-        <v>2068</v>
+        <v>2073</v>
       </c>
       <c r="F468" s="6" t="s">
-        <v>2069</v>
+        <v>2074</v>
       </c>
       <c r="I468" s="15" t="s">
-        <v>2070</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B469" s="2" t="s">
         <v>2072</v>
       </c>
-      <c r="B469" s="2" t="s">
+      <c r="D469" s="4" t="s">
         <v>2073</v>
       </c>
-      <c r="D469" s="4" t="s">
+      <c r="F469" s="6" t="s">
         <v>2074</v>
       </c>
-      <c r="F469" s="6" t="s">
+      <c r="I469" s="15" t="s">
         <v>2075</v>
-      </c>
-      <c r="I469" s="15" t="s">
-        <v>2076</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22988,30 +22993,30 @@
         <v>2083</v>
       </c>
       <c r="D471" s="4" t="s">
-        <v>2079</v>
+        <v>2084</v>
       </c>
       <c r="F471" s="6" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="I471" s="15" t="s">
-        <v>2081</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="B472" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D472" s="4" t="s">
+        <v>2084</v>
+      </c>
+      <c r="F472" s="6" t="s">
+        <v>2089</v>
+      </c>
+      <c r="I472" s="15" t="s">
         <v>2086</v>
-      </c>
-      <c r="D472" s="4" t="s">
-        <v>2087</v>
-      </c>
-      <c r="F472" s="6" t="s">
-        <v>2088</v>
-      </c>
-      <c r="I472" s="15" t="s">
-        <v>2089</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23028,24 +23033,24 @@
         <v>2093</v>
       </c>
       <c r="I473" s="15" t="s">
-        <v>203</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="D474" s="4" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="F474" s="6" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="I474" s="15" t="s">
-        <v>2098</v>
+        <v>203</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23070,33 +23075,33 @@
         <v>2104</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>2100</v>
+        <v>2105</v>
       </c>
       <c r="D476" s="4" t="s">
-        <v>2101</v>
+        <v>2106</v>
       </c>
       <c r="F476" s="6" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="I476" s="15" t="s">
-        <v>2103</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B477" s="2" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D477" s="4" t="s">
         <v>2106</v>
       </c>
-      <c r="B477" s="2" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D477" s="4" t="s">
+      <c r="F477" s="6" t="s">
+        <v>2110</v>
+      </c>
+      <c r="I477" s="15" t="s">
         <v>2108</v>
-      </c>
-      <c r="F477" s="6" t="s">
-        <v>2109</v>
-      </c>
-      <c r="I477" s="15" t="s">
-        <v>2110</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23110,32 +23115,32 @@
         <v>2113</v>
       </c>
       <c r="F478" s="6" t="s">
-        <v>2105</v>
+        <v>2114</v>
       </c>
       <c r="I478" s="15" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="479" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>2112</v>
+        <v>2117</v>
       </c>
       <c r="D479" s="4" t="s">
-        <v>2113</v>
+        <v>2118</v>
       </c>
       <c r="F479" s="6" t="s">
-        <v>2105</v>
+        <v>2110</v>
       </c>
       <c r="I479" s="15" t="s">
-        <v>2114</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>2116</v>
+        <v>2120</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>2117</v>
@@ -23144,10 +23149,10 @@
         <v>2118</v>
       </c>
       <c r="F480" s="6" t="s">
+        <v>2110</v>
+      </c>
+      <c r="I480" s="15" t="s">
         <v>2119</v>
-      </c>
-      <c r="I480" s="15" t="s">
-        <v>2120</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23155,50 +23160,50 @@
         <v>2121</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>2117</v>
+        <v>2122</v>
       </c>
       <c r="D481" s="4" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F481" s="6" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
       <c r="I481" s="15" t="s">
-        <v>2120</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B482" s="2" t="s">
         <v>2122</v>
       </c>
-      <c r="B482" s="2" t="s">
-        <v>2117</v>
-      </c>
       <c r="D482" s="4" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F482" s="6" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
       <c r="I482" s="15" t="s">
-        <v>2120</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D483" s="4" t="s">
         <v>2123</v>
       </c>
-      <c r="B483" s="2" t="s">
+      <c r="F483" s="6" t="s">
         <v>2124</v>
       </c>
-      <c r="D483" s="4" t="s">
+      <c r="I483" s="15" t="s">
         <v>2125</v>
-      </c>
-      <c r="F483" s="6" t="s">
-        <v>2126</v>
-      </c>
-      <c r="I483" s="15" t="s">
-        <v>2127</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23274,33 +23279,33 @@
         <v>2148</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>2144</v>
+        <v>2149</v>
       </c>
       <c r="D488" s="4" t="s">
-        <v>2145</v>
+        <v>2150</v>
       </c>
       <c r="F488" s="6" t="s">
-        <v>2146</v>
+        <v>2151</v>
       </c>
       <c r="I488" s="15" t="s">
-        <v>2147</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B489" s="2" t="s">
         <v>2149</v>
       </c>
-      <c r="B489" s="2" t="s">
+      <c r="D489" s="4" t="s">
         <v>2150</v>
       </c>
-      <c r="D489" s="4" t="s">
+      <c r="F489" s="6" t="s">
         <v>2151</v>
       </c>
-      <c r="F489" s="6" t="s">
+      <c r="I489" s="15" t="s">
         <v>2152</v>
-      </c>
-      <c r="I489" s="15" t="s">
-        <v>2153</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23325,33 +23330,33 @@
         <v>2159</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>2155</v>
+        <v>2160</v>
       </c>
       <c r="D491" s="4" t="s">
-        <v>2156</v>
+        <v>2161</v>
       </c>
       <c r="F491" s="6" t="s">
-        <v>2157</v>
+        <v>2162</v>
       </c>
       <c r="I491" s="15" t="s">
-        <v>2158</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B492" s="2" t="s">
         <v>2160</v>
       </c>
-      <c r="B492" s="2" t="s">
+      <c r="D492" s="4" t="s">
         <v>2161</v>
       </c>
-      <c r="D492" s="4" t="s">
+      <c r="F492" s="6" t="s">
         <v>2162</v>
       </c>
-      <c r="F492" s="6" t="s">
+      <c r="I492" s="15" t="s">
         <v>2163</v>
-      </c>
-      <c r="I492" s="15" t="s">
-        <v>2164</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23500,61 +23505,61 @@
       <c r="D501" s="4" t="s">
         <v>2207</v>
       </c>
+      <c r="F501" s="6" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I501" s="15" t="s">
+        <v>2209</v>
+      </c>
     </row>
     <row r="502" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="D502" s="4" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="D503" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>269</v>
+        <v>2217</v>
       </c>
       <c r="D504" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="F504" s="6" t="s">
-        <v>2215</v>
-      </c>
-      <c r="I504" s="15" t="s">
-        <v>272</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="s">
-        <v>2216</v>
+        <v>2219</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>2217</v>
+        <v>269</v>
       </c>
       <c r="D505" s="4" t="s">
-        <v>2218</v>
+        <v>270</v>
       </c>
       <c r="F505" s="6" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="I505" s="15" t="s">
-        <v>2220</v>
+        <v>272</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23568,27 +23573,27 @@
         <v>2223</v>
       </c>
       <c r="F506" s="6" t="s">
-        <v>2219</v>
+        <v>2224</v>
       </c>
       <c r="I506" s="15" t="s">
-        <v>2220</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D507" s="4" t="s">
+        <v>2228</v>
+      </c>
+      <c r="F507" s="6" t="s">
         <v>2224</v>
       </c>
-      <c r="B507" s="2" t="s">
+      <c r="I507" s="15" t="s">
         <v>2225</v>
-      </c>
-      <c r="D507" s="4" t="s">
-        <v>2226</v>
-      </c>
-      <c r="F507" s="6" t="s">
-        <v>2227</v>
-      </c>
-      <c r="I507" s="15" t="s">
-        <v>2228</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23596,67 +23601,67 @@
         <v>2229</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="D508" s="4" t="s">
-        <v>2226</v>
+        <v>2231</v>
       </c>
       <c r="F508" s="6" t="s">
-        <v>2227</v>
+        <v>2232</v>
       </c>
       <c r="I508" s="15" t="s">
-        <v>2228</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="1" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B509" s="2" t="s">
         <v>2230</v>
       </c>
-      <c r="B509" s="2" t="s">
-        <v>2225</v>
-      </c>
       <c r="D509" s="4" t="s">
-        <v>2226</v>
+        <v>2231</v>
       </c>
       <c r="F509" s="6" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="I509" s="15" t="s">
-        <v>2228</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="D510" s="4" t="s">
-        <v>2226</v>
+        <v>2231</v>
       </c>
       <c r="F510" s="6" t="s">
-        <v>2231</v>
+        <v>2236</v>
       </c>
       <c r="I510" s="15" t="s">
-        <v>2228</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="s">
-        <v>2233</v>
+        <v>2237</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>2234</v>
+        <v>2230</v>
       </c>
       <c r="D511" s="4" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="F511" s="6" t="s">
         <v>2236</v>
       </c>
       <c r="I511" s="15" t="s">
-        <v>2237</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="512" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23664,67 +23669,67 @@
         <v>2238</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>2234</v>
+        <v>2239</v>
       </c>
       <c r="D512" s="4" t="s">
-        <v>2235</v>
+        <v>2240</v>
       </c>
       <c r="F512" s="6" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="I512" s="15" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B513" s="2" t="s">
         <v>2239</v>
       </c>
-      <c r="B513" s="2" t="s">
-        <v>2234</v>
-      </c>
       <c r="D513" s="4" t="s">
-        <v>2235</v>
+        <v>2240</v>
       </c>
       <c r="F513" s="6" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="I513" s="15" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D514" s="4" t="s">
         <v>2240</v>
       </c>
-      <c r="B514" s="2" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D514" s="4" t="s">
-        <v>2235</v>
-      </c>
       <c r="F514" s="6" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="I514" s="15" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D515" s="4" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F515" s="6" t="s">
         <v>2241</v>
       </c>
-      <c r="B515" s="2" t="s">
+      <c r="I515" s="15" t="s">
         <v>2242</v>
-      </c>
-      <c r="D515" s="4" t="s">
-        <v>2243</v>
-      </c>
-      <c r="F515" s="6" t="s">
-        <v>2244</v>
-      </c>
-      <c r="I515" s="15" t="s">
-        <v>2245</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23783,38 +23788,38 @@
         <v>2261</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>274</v>
+        <v>2262</v>
       </c>
       <c r="D519" s="4" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="F519" s="6" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="I519" s="15" t="s">
-        <v>277</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D520" s="4" t="s">
-        <v>280</v>
+        <v>2267</v>
       </c>
       <c r="F520" s="6" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="I520" s="15" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="s">
-        <v>2266</v>
+        <v>2269</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>279</v>
@@ -23823,7 +23828,7 @@
         <v>280</v>
       </c>
       <c r="F521" s="6" t="s">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="I521" s="15" t="s">
         <v>282</v>
@@ -23831,41 +23836,41 @@
     </row>
     <row r="522" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="s">
-        <v>2267</v>
+        <v>2271</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D522" s="4" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="F522" s="6" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="I522" s="15" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="s">
-        <v>2269</v>
+        <v>2272</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D523" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F523" s="6" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
       <c r="I523" s="15" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>291</v>
@@ -23874,7 +23879,7 @@
         <v>292</v>
       </c>
       <c r="F524" s="6" t="s">
-        <v>2270</v>
+        <v>2275</v>
       </c>
       <c r="I524" s="15" t="s">
         <v>294</v>
@@ -23882,41 +23887,41 @@
     </row>
     <row r="525" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="1" t="s">
-        <v>2272</v>
+        <v>2276</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D525" s="4" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="F525" s="6" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="I525" s="15" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D526" s="4" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F526" s="6" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="I526" s="15" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>303</v>
@@ -23925,7 +23930,7 @@
         <v>304</v>
       </c>
       <c r="F527" s="6" t="s">
-        <v>2275</v>
+        <v>2280</v>
       </c>
       <c r="I527" s="15" t="s">
         <v>306</v>
@@ -23933,41 +23938,41 @@
     </row>
     <row r="528" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D528" s="4" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="F528" s="6" t="s">
-        <v>312</v>
+        <v>2280</v>
       </c>
       <c r="I528" s="15" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="s">
-        <v>2278</v>
+        <v>2282</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D529" s="4" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F529" s="6" t="s">
-        <v>2279</v>
+        <v>312</v>
       </c>
       <c r="I529" s="15" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
-        <v>2280</v>
+        <v>2283</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>315</v>
@@ -23976,7 +23981,7 @@
         <v>316</v>
       </c>
       <c r="F530" s="6" t="s">
-        <v>2279</v>
+        <v>2284</v>
       </c>
       <c r="I530" s="15" t="s">
         <v>318</v>
@@ -23984,19 +23989,19 @@
     </row>
     <row r="531" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="1" t="s">
-        <v>2281</v>
+        <v>2285</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>2282</v>
+        <v>315</v>
       </c>
       <c r="D531" s="4" t="s">
-        <v>2283</v>
+        <v>316</v>
       </c>
       <c r="F531" s="6" t="s">
         <v>2284</v>
       </c>
       <c r="I531" s="15" t="s">
-        <v>2285</v>
+        <v>318</v>
       </c>
     </row>
     <row r="532" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24089,74 +24094,74 @@
         <v>2311</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>2302</v>
+        <v>2312</v>
       </c>
       <c r="D537" s="4" t="s">
-        <v>2303</v>
+        <v>2313</v>
       </c>
       <c r="F537" s="6" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="I537" s="15" t="s">
-        <v>2305</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
-        <v>2313</v>
+        <v>2316</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>2314</v>
+        <v>2307</v>
       </c>
       <c r="D538" s="4" t="s">
-        <v>2315</v>
+        <v>2308</v>
       </c>
       <c r="F538" s="6" t="s">
-        <v>2316</v>
+        <v>2317</v>
+      </c>
+      <c r="I538" s="15" t="s">
+        <v>2310</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>2318</v>
+        <v>2319</v>
+      </c>
+      <c r="D539" s="4" t="s">
+        <v>2320</v>
+      </c>
+      <c r="F539" s="6" t="s">
+        <v>2321</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
-        <v>2319</v>
+        <v>2322</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>2320</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
-        <v>2321</v>
+        <v>2324</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>2322</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="542" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
-        <v>2323</v>
+        <v>2326</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>2324</v>
-      </c>
-      <c r="D542" s="4" t="s">
-        <v>2325</v>
-      </c>
-      <c r="F542" s="6" t="s">
-        <v>2326</v>
-      </c>
-      <c r="I542" s="15" t="s">
         <v>2327</v>
       </c>
     </row>
-    <row r="543" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="543" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="s">
         <v>2328</v>
       </c>
@@ -24164,40 +24169,40 @@
         <v>2329</v>
       </c>
       <c r="D543" s="4" t="s">
+        <v>2330</v>
+      </c>
+      <c r="F543" s="6" t="s">
+        <v>2331</v>
+      </c>
+      <c r="I543" s="15" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="544" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A544" s="1" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D544" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="F543" s="6" t="s">
-        <v>2330</v>
-      </c>
-      <c r="I543" s="15" t="s">
+      <c r="F544" s="6" t="s">
+        <v>2335</v>
+      </c>
+      <c r="I544" s="15" t="s">
         <v>347</v>
-      </c>
-    </row>
-    <row r="544" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A544" s="1" t="s">
-        <v>2331</v>
-      </c>
-      <c r="B544" s="2" t="s">
-        <v>2332</v>
-      </c>
-      <c r="D544" s="4" t="s">
-        <v>2333</v>
       </c>
     </row>
     <row r="545" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="D545" s="4" t="s">
-        <v>2336</v>
-      </c>
-      <c r="F545" s="6" t="s">
-        <v>2337</v>
-      </c>
-      <c r="I545" s="15" t="s">
         <v>2338</v>
       </c>
     </row>
@@ -24235,7 +24240,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="548" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="548" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
         <v>2349</v>
       </c>
@@ -24269,7 +24274,7 @@
         <v>2358</v>
       </c>
     </row>
-    <row r="550" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="550" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
         <v>2359</v>
       </c>
@@ -24487,27 +24492,27 @@
         <v>2422</v>
       </c>
       <c r="I562" s="15" t="s">
-        <v>2418</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="1" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>2425</v>
+      </c>
+      <c r="D563" s="4" t="s">
+        <v>2426</v>
+      </c>
+      <c r="F563" s="6" t="s">
+        <v>2427</v>
+      </c>
+      <c r="I563" s="15" t="s">
         <v>2423</v>
       </c>
-      <c r="B563" s="2" t="s">
-        <v>2424</v>
-      </c>
-      <c r="D563" s="4" t="s">
-        <v>2425</v>
-      </c>
-      <c r="F563" s="6" t="s">
-        <v>2426</v>
-      </c>
-      <c r="I563" s="15" t="s">
-        <v>2427</v>
-      </c>
-    </row>
-    <row r="564" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="564" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="s">
         <v>2428</v>
       </c>
@@ -24524,7 +24529,7 @@
         <v>2432</v>
       </c>
     </row>
-    <row r="565" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="565" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="s">
         <v>2433</v>
       </c>
@@ -24631,82 +24636,82 @@
         <v>2463</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>2459</v>
+        <v>2464</v>
       </c>
       <c r="D571" s="4" t="s">
-        <v>2460</v>
+        <v>2465</v>
       </c>
       <c r="F571" s="6" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
       <c r="I571" s="15" t="s">
-        <v>2462</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="572" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="1" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>2464</v>
+      </c>
+      <c r="D572" s="4" t="s">
         <v>2465</v>
       </c>
-      <c r="B572" s="2" t="s">
-        <v>2459</v>
-      </c>
-      <c r="D572" s="4" t="s">
-        <v>2460</v>
-      </c>
       <c r="F572" s="6" t="s">
-        <v>2464</v>
+        <v>2469</v>
       </c>
       <c r="I572" s="15" t="s">
-        <v>2462</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="s">
-        <v>2466</v>
+        <v>2470</v>
       </c>
       <c r="B573" s="2" t="s">
+        <v>2464</v>
+      </c>
+      <c r="D573" s="4" t="s">
+        <v>2465</v>
+      </c>
+      <c r="F573" s="6" t="s">
+        <v>2469</v>
+      </c>
+      <c r="I573" s="15" t="s">
         <v>2467</v>
-      </c>
-      <c r="D573" s="4" t="s">
-        <v>2468</v>
       </c>
     </row>
     <row r="574" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="D574" s="4" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="575" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="D575" s="4" t="s">
-        <v>2474</v>
-      </c>
-    </row>
-    <row r="576" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="576" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="D576" s="4" t="s">
-        <v>2477</v>
-      </c>
-      <c r="F576" s="6" t="s">
-        <v>2478</v>
-      </c>
-      <c r="I576" s="15" t="s">
         <v>2479</v>
       </c>
     </row>
@@ -25165,7 +25170,7 @@
       <c r="F603" s="6" t="s">
         <v>2613</v>
       </c>
-      <c r="I603" s="7" t="s">
+      <c r="I603" s="15" t="s">
         <v>2614</v>
       </c>
     </row>
@@ -25203,7 +25208,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="606" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="606" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A606" s="1" t="s">
         <v>2625</v>
       </c>
@@ -25213,32 +25218,32 @@
       <c r="D606" s="4" t="s">
         <v>2627</v>
       </c>
+      <c r="F606" s="6" t="s">
+        <v>2628</v>
+      </c>
+      <c r="I606" s="7" t="s">
+        <v>2629</v>
+      </c>
     </row>
     <row r="607" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="s">
-        <v>2628</v>
+        <v>2630</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>2629</v>
+        <v>2631</v>
       </c>
       <c r="D607" s="4" t="s">
-        <v>2630</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="608" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A608" s="1" t="s">
-        <v>2631</v>
+        <v>2633</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>2632</v>
+        <v>2634</v>
       </c>
       <c r="D608" s="4" t="s">
-        <v>2633</v>
-      </c>
-      <c r="F608" s="6" t="s">
-        <v>2634</v>
-      </c>
-      <c r="I608" s="15" t="s">
         <v>2635</v>
       </c>
     </row>
@@ -25358,24 +25363,24 @@
         <v>2669</v>
       </c>
       <c r="I615" s="15" t="s">
-        <v>464</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="616" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="s">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>2671</v>
+        <v>2672</v>
       </c>
       <c r="D616" s="4" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="F616" s="6" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="I616" s="15" t="s">
-        <v>2674</v>
+        <v>464</v>
       </c>
     </row>
     <row r="617" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25391,7 +25396,7 @@
       <c r="F617" s="6" t="s">
         <v>2678</v>
       </c>
-      <c r="I617" s="16" t="s">
+      <c r="I617" s="15" t="s">
         <v>2679</v>
       </c>
     </row>
@@ -25400,87 +25405,87 @@
         <v>2680</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>2676</v>
+        <v>2681</v>
       </c>
       <c r="D618" s="4" t="s">
-        <v>2677</v>
+        <v>2682</v>
       </c>
       <c r="F618" s="6" t="s">
-        <v>2678</v>
-      </c>
-      <c r="I618" s="16" t="s">
-        <v>2679</v>
+        <v>2683</v>
+      </c>
+      <c r="I618" s="15" t="s">
+        <v>2684</v>
       </c>
     </row>
     <row r="619" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A619" s="1" t="s">
+        <v>2685</v>
+      </c>
+      <c r="B619" s="2" t="s">
         <v>2681</v>
       </c>
-      <c r="B619" s="2" t="s">
-        <v>2676</v>
-      </c>
       <c r="D619" s="4" t="s">
-        <v>2677</v>
+        <v>2682</v>
       </c>
       <c r="F619" s="6" t="s">
-        <v>2678</v>
-      </c>
-      <c r="I619" s="16" t="s">
-        <v>2679</v>
+        <v>2683</v>
+      </c>
+      <c r="I619" s="15" t="s">
+        <v>2684</v>
       </c>
     </row>
     <row r="620" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A620" s="1" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>2681</v>
+      </c>
+      <c r="D620" s="4" t="s">
         <v>2682</v>
       </c>
-      <c r="B620" s="2" t="s">
-        <v>2676</v>
-      </c>
-      <c r="D620" s="4" t="s">
-        <v>2677</v>
-      </c>
       <c r="F620" s="6" t="s">
-        <v>2678</v>
-      </c>
-      <c r="I620" s="16" t="s">
-        <v>2679</v>
+        <v>2683</v>
+      </c>
+      <c r="I620" s="15" t="s">
+        <v>2684</v>
       </c>
     </row>
     <row r="621" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A621" s="1" t="s">
+        <v>2687</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>2681</v>
+      </c>
+      <c r="D621" s="4" t="s">
+        <v>2682</v>
+      </c>
+      <c r="F621" s="6" t="s">
         <v>2683</v>
       </c>
-      <c r="B621" s="2" t="s">
-        <v>2676</v>
-      </c>
-      <c r="D621" s="4" t="s">
-        <v>2677</v>
-      </c>
-      <c r="F621" s="6" t="s">
-        <v>2678</v>
-      </c>
-      <c r="I621" s="16" t="s">
-        <v>2679</v>
-      </c>
-    </row>
-    <row r="622" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I621" s="15" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="622" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="s">
+        <v>2688</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>2681</v>
+      </c>
+      <c r="D622" s="4" t="s">
+        <v>2682</v>
+      </c>
+      <c r="F622" s="6" t="s">
+        <v>2683</v>
+      </c>
+      <c r="I622" s="15" t="s">
         <v>2684</v>
       </c>
-      <c r="B622" s="2" t="s">
-        <v>2685</v>
-      </c>
-      <c r="D622" s="4" t="s">
-        <v>2686</v>
-      </c>
-      <c r="F622" s="6" t="s">
-        <v>2687</v>
-      </c>
-      <c r="I622" s="15" t="s">
-        <v>2688</v>
-      </c>
-    </row>
-    <row r="623" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="623" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A623" s="1" t="s">
         <v>2689</v>
       </c>
@@ -25570,30 +25575,30 @@
         <v>2714</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>485</v>
+        <v>2715</v>
       </c>
       <c r="D628" s="4" t="s">
-        <v>486</v>
+        <v>2716</v>
       </c>
       <c r="F628" s="6" t="s">
-        <v>487</v>
+        <v>2717</v>
       </c>
       <c r="I628" s="15" t="s">
-        <v>2715</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="629" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A629" s="1" t="s">
-        <v>2716</v>
+        <v>2719</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>2717</v>
+        <v>485</v>
       </c>
       <c r="D629" s="4" t="s">
-        <v>2718</v>
+        <v>486</v>
       </c>
       <c r="F629" s="6" t="s">
-        <v>2719</v>
+        <v>487</v>
       </c>
       <c r="I629" s="15" t="s">
         <v>2720</v>
@@ -25672,33 +25677,33 @@
         <v>2741</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>2737</v>
+        <v>2742</v>
       </c>
       <c r="D634" s="4" t="s">
-        <v>2738</v>
+        <v>2743</v>
       </c>
       <c r="F634" s="6" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="I634" s="15" t="s">
-        <v>2740</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="635" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A635" s="1" t="s">
+        <v>2746</v>
+      </c>
+      <c r="B635" s="2" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D635" s="4" t="s">
         <v>2743</v>
       </c>
-      <c r="B635" s="2" t="s">
-        <v>2744</v>
-      </c>
-      <c r="D635" s="4" t="s">
+      <c r="F635" s="6" t="s">
+        <v>2747</v>
+      </c>
+      <c r="I635" s="15" t="s">
         <v>2745</v>
-      </c>
-      <c r="F635" s="6" t="s">
-        <v>2746</v>
-      </c>
-      <c r="I635" s="15" t="s">
-        <v>2747</v>
       </c>
     </row>
     <row r="636" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25706,50 +25711,50 @@
         <v>2748</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>2744</v>
+        <v>2749</v>
       </c>
       <c r="D636" s="4" t="s">
-        <v>2745</v>
+        <v>2750</v>
       </c>
       <c r="F636" s="6" t="s">
-        <v>2746</v>
+        <v>2751</v>
       </c>
       <c r="I636" s="15" t="s">
-        <v>2747</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="637" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A637" s="1" t="s">
+        <v>2753</v>
+      </c>
+      <c r="B637" s="2" t="s">
         <v>2749</v>
       </c>
-      <c r="B637" s="2" t="s">
-        <v>2744</v>
-      </c>
       <c r="D637" s="4" t="s">
-        <v>2745</v>
+        <v>2750</v>
       </c>
       <c r="F637" s="6" t="s">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="I637" s="15" t="s">
-        <v>2747</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="638" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A638" s="1" t="s">
-        <v>2751</v>
+        <v>2754</v>
       </c>
       <c r="B638" s="2" t="s">
+        <v>2749</v>
+      </c>
+      <c r="D638" s="4" t="s">
+        <v>2750</v>
+      </c>
+      <c r="F638" s="6" t="s">
+        <v>2755</v>
+      </c>
+      <c r="I638" s="15" t="s">
         <v>2752</v>
-      </c>
-      <c r="D638" s="4" t="s">
-        <v>2753</v>
-      </c>
-      <c r="F638" s="6" t="s">
-        <v>2754</v>
-      </c>
-      <c r="I638" s="15" t="s">
-        <v>2755</v>
       </c>
     </row>
     <row r="639" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25757,84 +25762,84 @@
         <v>2756</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>2752</v>
+        <v>2757</v>
       </c>
       <c r="D639" s="4" t="s">
-        <v>2753</v>
+        <v>2758</v>
       </c>
       <c r="F639" s="6" t="s">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="I639" s="15" t="s">
-        <v>2755</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="640" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A640" s="1" t="s">
+        <v>2761</v>
+      </c>
+      <c r="B640" s="2" t="s">
         <v>2757</v>
       </c>
-      <c r="B640" s="2" t="s">
-        <v>2752</v>
-      </c>
       <c r="D640" s="4" t="s">
-        <v>2753</v>
+        <v>2758</v>
       </c>
       <c r="F640" s="6" t="s">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="I640" s="15" t="s">
-        <v>2755</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="641" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="s">
+        <v>2762</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>2757</v>
+      </c>
+      <c r="D641" s="4" t="s">
         <v>2758</v>
       </c>
-      <c r="B641" s="2" t="s">
-        <v>2752</v>
-      </c>
-      <c r="D641" s="4" t="s">
-        <v>2753</v>
-      </c>
       <c r="F641" s="6" t="s">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="I641" s="15" t="s">
-        <v>2755</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="642" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A642" s="1" t="s">
+        <v>2763</v>
+      </c>
+      <c r="B642" s="2" t="s">
+        <v>2757</v>
+      </c>
+      <c r="D642" s="4" t="s">
+        <v>2758</v>
+      </c>
+      <c r="F642" s="6" t="s">
         <v>2759</v>
       </c>
-      <c r="B642" s="2" t="s">
-        <v>2752</v>
-      </c>
-      <c r="D642" s="4" t="s">
-        <v>2753</v>
-      </c>
-      <c r="F642" s="6" t="s">
-        <v>2754</v>
-      </c>
       <c r="I642" s="15" t="s">
-        <v>2755</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="643" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A643" s="1" t="s">
+        <v>2764</v>
+      </c>
+      <c r="B643" s="2" t="s">
+        <v>2757</v>
+      </c>
+      <c r="D643" s="4" t="s">
+        <v>2758</v>
+      </c>
+      <c r="F643" s="6" t="s">
+        <v>2759</v>
+      </c>
+      <c r="I643" s="15" t="s">
         <v>2760</v>
-      </c>
-      <c r="B643" s="2" t="s">
-        <v>2761</v>
-      </c>
-      <c r="D643" s="4" t="s">
-        <v>2762</v>
-      </c>
-      <c r="F643" s="6" t="s">
-        <v>2763</v>
-      </c>
-      <c r="I643" s="15" t="s">
-        <v>2764</v>
       </c>
     </row>
     <row r="644" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25842,76 +25847,76 @@
         <v>2765</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>2761</v>
+        <v>2766</v>
       </c>
       <c r="D644" s="4" t="s">
-        <v>2762</v>
+        <v>2767</v>
       </c>
       <c r="F644" s="6" t="s">
-        <v>2763</v>
+        <v>2768</v>
       </c>
       <c r="I644" s="15" t="s">
-        <v>2764</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="645" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="s">
+        <v>2770</v>
+      </c>
+      <c r="B645" s="2" t="s">
         <v>2766</v>
       </c>
-      <c r="B645" s="2" t="s">
+      <c r="D645" s="4" t="s">
         <v>2767</v>
       </c>
-      <c r="D645" s="4" t="s">
+      <c r="F645" s="6" t="s">
         <v>2768</v>
+      </c>
+      <c r="I645" s="15" t="s">
+        <v>2769</v>
       </c>
     </row>
     <row r="646" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A646" s="1" t="s">
-        <v>2769</v>
+        <v>2771</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>2770</v>
+        <v>2772</v>
       </c>
       <c r="D646" s="4" t="s">
-        <v>2771</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="647" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A647" s="1" t="s">
-        <v>2772</v>
+        <v>2774</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>2770</v>
+        <v>2775</v>
       </c>
       <c r="D647" s="4" t="s">
-        <v>2771</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="648" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A648" s="1" t="s">
-        <v>2773</v>
+        <v>2777</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>2774</v>
+        <v>2775</v>
       </c>
       <c r="D648" s="4" t="s">
-        <v>2775</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="649" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="s">
-        <v>2776</v>
+        <v>2778</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>2777</v>
+        <v>2779</v>
       </c>
       <c r="D649" s="4" t="s">
-        <v>2778</v>
-      </c>
-      <c r="F649" s="6" t="s">
-        <v>2779</v>
-      </c>
-      <c r="I649" s="15" t="s">
         <v>2780</v>
       </c>
     </row>
@@ -25959,43 +25964,43 @@
       <c r="D652" s="4" t="s">
         <v>2793</v>
       </c>
+      <c r="F652" s="6" t="s">
+        <v>2794</v>
+      </c>
+      <c r="I652" s="15" t="s">
+        <v>2795</v>
+      </c>
     </row>
     <row r="653" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A653" s="1" t="s">
-        <v>2794</v>
+        <v>2796</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>2795</v>
+        <v>2797</v>
       </c>
       <c r="D653" s="4" t="s">
-        <v>2796</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="654" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A654" s="1" t="s">
-        <v>2797</v>
+        <v>2799</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>2798</v>
+        <v>2800</v>
       </c>
       <c r="D654" s="4" t="s">
-        <v>2799</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="655" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A655" s="1" t="s">
-        <v>2800</v>
+        <v>2802</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>2801</v>
+        <v>2803</v>
       </c>
       <c r="D655" s="4" t="s">
-        <v>2802</v>
-      </c>
-      <c r="F655" s="6" t="s">
-        <v>2803</v>
-      </c>
-      <c r="I655" s="15" t="s">
         <v>2804</v>
       </c>
     </row>
@@ -26089,33 +26094,33 @@
         <v>2830</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>2826</v>
+        <v>2831</v>
       </c>
       <c r="D661" s="4" t="s">
-        <v>2827</v>
+        <v>2832</v>
       </c>
       <c r="F661" s="6" t="s">
-        <v>2828</v>
+        <v>2833</v>
       </c>
       <c r="I661" s="15" t="s">
-        <v>2829</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="662" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A662" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B662" s="2" t="s">
         <v>2831</v>
       </c>
-      <c r="B662" s="2" t="s">
+      <c r="D662" s="4" t="s">
         <v>2832</v>
       </c>
-      <c r="D662" s="4" t="s">
+      <c r="F662" s="6" t="s">
         <v>2833</v>
       </c>
-      <c r="F662" s="6" t="s">
+      <c r="I662" s="15" t="s">
         <v>2834</v>
-      </c>
-      <c r="I662" s="15" t="s">
-        <v>2835</v>
       </c>
     </row>
     <row r="663" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26140,33 +26145,33 @@
         <v>2841</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>2837</v>
+        <v>2842</v>
       </c>
       <c r="D664" s="4" t="s">
-        <v>2838</v>
+        <v>2843</v>
       </c>
       <c r="F664" s="6" t="s">
-        <v>2839</v>
+        <v>2844</v>
       </c>
       <c r="I664" s="15" t="s">
-        <v>2840</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="665" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A665" s="1" t="s">
+        <v>2846</v>
+      </c>
+      <c r="B665" s="2" t="s">
         <v>2842</v>
       </c>
-      <c r="B665" s="2" t="s">
+      <c r="D665" s="4" t="s">
         <v>2843</v>
       </c>
-      <c r="D665" s="4" t="s">
+      <c r="F665" s="6" t="s">
         <v>2844</v>
       </c>
-      <c r="F665" s="6" t="s">
+      <c r="I665" s="15" t="s">
         <v>2845</v>
-      </c>
-      <c r="I665" s="15" t="s">
-        <v>2846</v>
       </c>
     </row>
     <row r="666" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26250,24 +26255,24 @@
       <c r="F670" s="6" t="s">
         <v>2870</v>
       </c>
-      <c r="I670" s="15"/>
+      <c r="I670" s="15" t="s">
+        <v>2871</v>
+      </c>
     </row>
     <row r="671" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A671" s="1" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="D671" s="4" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="F671" s="6" t="s">
-        <v>2874</v>
-      </c>
-      <c r="I671" s="15" t="s">
         <v>2875</v>
       </c>
+      <c r="I671" s="15"/>
     </row>
     <row r="672" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A672" s="1" t="s">
@@ -26342,50 +26347,50 @@
         <v>2896</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>606</v>
+        <v>2897</v>
       </c>
       <c r="D676" s="4" t="s">
-        <v>607</v>
+        <v>2898</v>
       </c>
       <c r="F676" s="6" t="s">
-        <v>608</v>
+        <v>2899</v>
       </c>
       <c r="I676" s="15" t="s">
-        <v>2897</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="677" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A677" s="1" t="s">
-        <v>2898</v>
+        <v>2901</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>2892</v>
+        <v>606</v>
       </c>
       <c r="D677" s="4" t="s">
-        <v>2893</v>
+        <v>607</v>
       </c>
       <c r="F677" s="6" t="s">
-        <v>2894</v>
+        <v>608</v>
       </c>
       <c r="I677" s="15" t="s">
-        <v>2895</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="678" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A678" s="1" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>2897</v>
+      </c>
+      <c r="D678" s="4" t="s">
+        <v>2898</v>
+      </c>
+      <c r="F678" s="6" t="s">
         <v>2899</v>
       </c>
-      <c r="B678" s="2" t="s">
+      <c r="I678" s="15" t="s">
         <v>2900</v>
-      </c>
-      <c r="D678" s="4" t="s">
-        <v>2901</v>
-      </c>
-      <c r="F678" s="6" t="s">
-        <v>2902</v>
-      </c>
-      <c r="I678" s="15" t="s">
-        <v>2903</v>
       </c>
     </row>
     <row r="679" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26410,30 +26415,30 @@
         <v>2909</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>2900</v>
+        <v>2910</v>
       </c>
       <c r="D680" s="4" t="s">
-        <v>2901</v>
+        <v>2911</v>
       </c>
       <c r="F680" s="6" t="s">
-        <v>2902</v>
+        <v>2912</v>
       </c>
       <c r="I680" s="15" t="s">
-        <v>2910</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="681" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A681" s="1" t="s">
-        <v>2911</v>
+        <v>2914</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>2912</v>
+        <v>2905</v>
       </c>
       <c r="D681" s="4" t="s">
-        <v>2913</v>
+        <v>2906</v>
       </c>
       <c r="F681" s="6" t="s">
-        <v>2914</v>
+        <v>2907</v>
       </c>
       <c r="I681" s="15" t="s">
         <v>2915</v>
@@ -26623,24 +26628,24 @@
         <v>2969</v>
       </c>
       <c r="I692" s="15" t="s">
-        <v>2965</v>
-      </c>
-    </row>
-    <row r="693" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="693" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A693" s="1" t="s">
+        <v>2971</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>2972</v>
+      </c>
+      <c r="D693" s="4" t="s">
+        <v>2973</v>
+      </c>
+      <c r="F693" s="6" t="s">
+        <v>2974</v>
+      </c>
+      <c r="I693" s="15" t="s">
         <v>2970</v>
-      </c>
-      <c r="B693" s="2" t="s">
-        <v>2971</v>
-      </c>
-      <c r="D693" s="4" t="s">
-        <v>2972</v>
-      </c>
-      <c r="F693" s="6" t="s">
-        <v>2973</v>
-      </c>
-      <c r="I693" s="15" t="s">
-        <v>2974</v>
       </c>
     </row>
     <row r="694" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26648,33 +26653,33 @@
         <v>2975</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>2971</v>
+        <v>2976</v>
       </c>
       <c r="D694" s="4" t="s">
-        <v>2972</v>
+        <v>2977</v>
       </c>
       <c r="F694" s="6" t="s">
-        <v>2973</v>
+        <v>2978</v>
       </c>
       <c r="I694" s="15" t="s">
-        <v>2974</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="695" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A695" s="1" t="s">
+        <v>2980</v>
+      </c>
+      <c r="B695" s="2" t="s">
         <v>2976</v>
       </c>
-      <c r="B695" s="2" t="s">
+      <c r="D695" s="4" t="s">
         <v>2977</v>
       </c>
-      <c r="D695" s="4" t="s">
+      <c r="F695" s="6" t="s">
         <v>2978</v>
       </c>
-      <c r="F695" s="6" t="s">
+      <c r="I695" s="15" t="s">
         <v>2979</v>
-      </c>
-      <c r="I695" s="15" t="s">
-        <v>2980</v>
       </c>
     </row>
     <row r="696" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26682,33 +26687,33 @@
         <v>2981</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>2977</v>
+        <v>2982</v>
       </c>
       <c r="D696" s="4" t="s">
-        <v>2978</v>
+        <v>2983</v>
       </c>
       <c r="F696" s="6" t="s">
-        <v>2979</v>
+        <v>2984</v>
       </c>
       <c r="I696" s="15" t="s">
-        <v>2980</v>
-      </c>
-    </row>
-    <row r="697" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2985</v>
+      </c>
+    </row>
+    <row r="697" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A697" s="1" t="s">
+        <v>2986</v>
+      </c>
+      <c r="B697" s="2" t="s">
         <v>2982</v>
       </c>
-      <c r="B697" s="2" t="s">
+      <c r="D697" s="4" t="s">
         <v>2983</v>
       </c>
-      <c r="D697" s="4" t="s">
+      <c r="F697" s="6" t="s">
         <v>2984</v>
       </c>
-      <c r="F697" s="6" t="s">
+      <c r="I697" s="15" t="s">
         <v>2985</v>
-      </c>
-      <c r="I697" s="15" t="s">
-        <v>2986</v>
       </c>
     </row>
     <row r="698" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26733,33 +26738,33 @@
         <v>2992</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>2988</v>
+        <v>2993</v>
       </c>
       <c r="D699" s="4" t="s">
-        <v>2989</v>
+        <v>2994</v>
       </c>
       <c r="F699" s="6" t="s">
-        <v>2990</v>
+        <v>2995</v>
       </c>
       <c r="I699" s="15" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="700" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A700" s="1" t="s">
+        <v>2997</v>
+      </c>
+      <c r="B700" s="2" t="s">
         <v>2993</v>
       </c>
-      <c r="B700" s="2" t="s">
+      <c r="D700" s="4" t="s">
         <v>2994</v>
       </c>
-      <c r="D700" s="4" t="s">
+      <c r="F700" s="6" t="s">
         <v>2995</v>
       </c>
-      <c r="F700" s="6" t="s">
+      <c r="I700" s="15" t="s">
         <v>2996</v>
-      </c>
-      <c r="I700" s="15" t="s">
-        <v>2997</v>
       </c>
     </row>
     <row r="701" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26801,33 +26806,33 @@
         <v>3008</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>3004</v>
+        <v>3009</v>
       </c>
       <c r="D703" s="4" t="s">
-        <v>3005</v>
+        <v>3010</v>
       </c>
       <c r="F703" s="6" t="s">
-        <v>3006</v>
+        <v>3011</v>
       </c>
       <c r="I703" s="15" t="s">
-        <v>3007</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="704" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A704" s="1" t="s">
+        <v>3013</v>
+      </c>
+      <c r="B704" s="2" t="s">
         <v>3009</v>
       </c>
-      <c r="B704" s="2" t="s">
+      <c r="D704" s="4" t="s">
         <v>3010</v>
       </c>
-      <c r="D704" s="4" t="s">
+      <c r="F704" s="6" t="s">
         <v>3011</v>
       </c>
-      <c r="F704" s="6" t="s">
+      <c r="I704" s="15" t="s">
         <v>3012</v>
-      </c>
-      <c r="I704" s="15" t="s">
-        <v>3013</v>
       </c>
     </row>
     <row r="705" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27163,47 +27168,47 @@
       <c r="D724" s="4" t="s">
         <v>3111</v>
       </c>
+      <c r="F724" s="6" t="s">
+        <v>3112</v>
+      </c>
+      <c r="I724" s="15" t="s">
+        <v>3113</v>
+      </c>
     </row>
     <row r="725" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A725" s="1" t="s">
-        <v>3112</v>
+        <v>3114</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>3113</v>
+        <v>3115</v>
       </c>
       <c r="D725" s="4" t="s">
-        <v>3114</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="726" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A726" s="1" t="s">
-        <v>3115</v>
+        <v>3117</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>3116</v>
+        <v>3118</v>
       </c>
       <c r="D726" s="4" t="s">
-        <v>3117</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="727" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A727" s="1" t="s">
-        <v>3118</v>
+        <v>3120</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>3119</v>
+        <v>3121</v>
       </c>
       <c r="D727" s="4" t="s">
-        <v>3120</v>
-      </c>
-      <c r="F727" s="6" t="s">
-        <v>3121</v>
-      </c>
-      <c r="I727" s="15" t="s">
         <v>3122</v>
       </c>
     </row>
-    <row r="728" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="728" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A728" s="1" t="s">
         <v>3123</v>
       </c>
@@ -27220,7 +27225,7 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="729" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="729" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A729" s="1" t="s">
         <v>3128</v>
       </c>
@@ -27292,60 +27297,60 @@
       <c r="A733" s="1" t="s">
         <v>3148</v>
       </c>
-      <c r="B733" s="1" t="s">
+      <c r="B733" s="2" t="s">
         <v>3149</v>
       </c>
       <c r="D733" s="4" t="s">
         <v>3150</v>
       </c>
+      <c r="F733" s="6" t="s">
+        <v>3151</v>
+      </c>
+      <c r="I733" s="15" t="s">
+        <v>3152</v>
+      </c>
     </row>
     <row r="734" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A734" s="1" t="s">
-        <v>3151</v>
+        <v>3153</v>
       </c>
       <c r="B734" s="1" t="s">
-        <v>3152</v>
+        <v>3154</v>
       </c>
       <c r="D734" s="4" t="s">
-        <v>3153</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="735" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A735" s="1" t="s">
-        <v>3154</v>
+        <v>3156</v>
       </c>
       <c r="B735" s="1" t="s">
-        <v>3155</v>
+        <v>3157</v>
       </c>
       <c r="D735" s="4" t="s">
-        <v>3156</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="736" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A736" s="1" t="s">
-        <v>3157</v>
+        <v>3159</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>3158</v>
+        <v>3160</v>
       </c>
       <c r="D736" s="4" t="s">
-        <v>3159</v>
-      </c>
-    </row>
-    <row r="737" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3161</v>
+      </c>
+    </row>
+    <row r="737" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A737" s="1" t="s">
-        <v>3160</v>
-      </c>
-      <c r="B737" s="2" t="s">
-        <v>3161</v>
+        <v>3162</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>3163</v>
       </c>
       <c r="D737" s="4" t="s">
-        <v>3162</v>
-      </c>
-      <c r="F737" s="6" t="s">
-        <v>3163</v>
-      </c>
-      <c r="I737" s="7" t="s">
         <v>3164</v>
       </c>
     </row>
@@ -27383,7 +27388,7 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="740" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="740" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A740" s="1" t="s">
         <v>3175</v>
       </c>
@@ -27396,7 +27401,7 @@
       <c r="F740" s="6" t="s">
         <v>3178</v>
       </c>
-      <c r="I740" s="15" t="s">
+      <c r="I740" s="7" t="s">
         <v>3179</v>
       </c>
     </row>
@@ -27476,30 +27481,30 @@
         <v>3201</v>
       </c>
       <c r="D745" s="4" t="s">
-        <v>3197</v>
+        <v>3202</v>
       </c>
       <c r="F745" s="6" t="s">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="I745" s="15" t="s">
-        <v>3199</v>
+        <v>3204</v>
       </c>
     </row>
     <row r="746" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A746" s="1" t="s">
-        <v>3203</v>
+        <v>3205</v>
       </c>
       <c r="B746" s="2" t="s">
+        <v>3206</v>
+      </c>
+      <c r="D746" s="4" t="s">
+        <v>3202</v>
+      </c>
+      <c r="F746" s="6" t="s">
+        <v>3207</v>
+      </c>
+      <c r="I746" s="15" t="s">
         <v>3204</v>
-      </c>
-      <c r="D746" s="4" t="s">
-        <v>3205</v>
-      </c>
-      <c r="F746" s="6" t="s">
-        <v>3206</v>
-      </c>
-      <c r="I746" s="15" t="s">
-        <v>3207</v>
       </c>
     </row>
     <row r="747" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27524,33 +27529,33 @@
         <v>3213</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>3209</v>
+        <v>3214</v>
       </c>
       <c r="D748" s="4" t="s">
-        <v>3210</v>
+        <v>3215</v>
       </c>
       <c r="F748" s="6" t="s">
-        <v>3211</v>
+        <v>3216</v>
       </c>
       <c r="I748" s="15" t="s">
-        <v>3212</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="749" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A749" s="1" t="s">
+        <v>3218</v>
+      </c>
+      <c r="B749" s="2" t="s">
         <v>3214</v>
       </c>
-      <c r="B749" s="2" t="s">
+      <c r="D749" s="4" t="s">
         <v>3215</v>
       </c>
-      <c r="D749" s="4" t="s">
+      <c r="F749" s="6" t="s">
         <v>3216</v>
       </c>
-      <c r="F749" s="6" t="s">
+      <c r="I749" s="15" t="s">
         <v>3217</v>
-      </c>
-      <c r="I749" s="15" t="s">
-        <v>3218</v>
       </c>
     </row>
     <row r="750" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27643,33 +27648,33 @@
         <v>3244</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>3240</v>
+        <v>3245</v>
       </c>
       <c r="D755" s="4" t="s">
-        <v>3241</v>
+        <v>3246</v>
       </c>
       <c r="F755" s="6" t="s">
-        <v>3242</v>
+        <v>3247</v>
       </c>
       <c r="I755" s="15" t="s">
-        <v>3243</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="756" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A756" s="1" t="s">
+        <v>3249</v>
+      </c>
+      <c r="B756" s="2" t="s">
         <v>3245</v>
       </c>
-      <c r="B756" s="2" t="s">
+      <c r="D756" s="4" t="s">
         <v>3246</v>
       </c>
-      <c r="D756" s="4" t="s">
+      <c r="F756" s="6" t="s">
         <v>3247</v>
       </c>
-      <c r="F756" s="6" t="s">
+      <c r="I756" s="15" t="s">
         <v>3248</v>
-      </c>
-      <c r="I756" s="15" t="s">
-        <v>3249</v>
       </c>
     </row>
     <row r="757" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27728,33 +27733,33 @@
         <v>3265</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>3261</v>
+        <v>3266</v>
       </c>
       <c r="D760" s="4" t="s">
-        <v>3262</v>
+        <v>3267</v>
       </c>
       <c r="F760" s="6" t="s">
-        <v>3263</v>
+        <v>3268</v>
       </c>
       <c r="I760" s="15" t="s">
-        <v>3264</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="761" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A761" s="1" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B761" s="2" t="s">
         <v>3266</v>
       </c>
-      <c r="B761" s="2" t="s">
+      <c r="D761" s="4" t="s">
         <v>3267</v>
       </c>
-      <c r="D761" s="4" t="s">
+      <c r="F761" s="6" t="s">
         <v>3268</v>
       </c>
-      <c r="F761" s="6" t="s">
+      <c r="I761" s="15" t="s">
         <v>3269</v>
-      </c>
-      <c r="I761" s="15" t="s">
-        <v>3270</v>
       </c>
     </row>
     <row r="762" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27813,33 +27818,33 @@
         <v>3286</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>3282</v>
+        <v>3287</v>
       </c>
       <c r="D765" s="4" t="s">
-        <v>3283</v>
+        <v>3288</v>
       </c>
       <c r="F765" s="6" t="s">
-        <v>3284</v>
+        <v>3289</v>
       </c>
       <c r="I765" s="15" t="s">
-        <v>3285</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="766" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A766" s="1" t="s">
+        <v>3291</v>
+      </c>
+      <c r="B766" s="2" t="s">
         <v>3287</v>
       </c>
-      <c r="B766" s="2" t="s">
+      <c r="D766" s="4" t="s">
         <v>3288</v>
       </c>
-      <c r="D766" s="4" t="s">
+      <c r="F766" s="6" t="s">
         <v>3289</v>
       </c>
-      <c r="F766" s="6" t="s">
+      <c r="I766" s="15" t="s">
         <v>3290</v>
-      </c>
-      <c r="I766" s="15" t="s">
-        <v>3291</v>
       </c>
     </row>
     <row r="767" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27898,33 +27903,33 @@
         <v>3307</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>3303</v>
+        <v>3308</v>
       </c>
       <c r="D770" s="4" t="s">
-        <v>3304</v>
+        <v>3309</v>
       </c>
       <c r="F770" s="6" t="s">
-        <v>3305</v>
+        <v>3310</v>
       </c>
       <c r="I770" s="15" t="s">
-        <v>3306</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="771" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A771" s="1" t="s">
+        <v>3312</v>
+      </c>
+      <c r="B771" s="2" t="s">
         <v>3308</v>
       </c>
-      <c r="B771" s="2" t="s">
+      <c r="D771" s="4" t="s">
         <v>3309</v>
       </c>
-      <c r="D771" s="4" t="s">
+      <c r="F771" s="6" t="s">
         <v>3310</v>
       </c>
-      <c r="F771" s="6" t="s">
+      <c r="I771" s="15" t="s">
         <v>3311</v>
-      </c>
-      <c r="I771" s="15" t="s">
-        <v>3312</v>
       </c>
     </row>
     <row r="772" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28114,7 +28119,7 @@
         <v>3367</v>
       </c>
     </row>
-    <row r="783" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="783" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A783" s="1" t="s">
         <v>3368</v>
       </c>
@@ -28148,7 +28153,7 @@
         <v>3377</v>
       </c>
     </row>
-    <row r="785" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="785" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A785" s="1" t="s">
         <v>3378</v>
       </c>
@@ -28165,7 +28170,7 @@
         <v>3382</v>
       </c>
     </row>
-    <row r="786" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="786" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A786" s="1" t="s">
         <v>3383</v>
       </c>
@@ -28199,7 +28204,7 @@
         <v>3392</v>
       </c>
     </row>
-    <row r="788" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="788" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A788" s="1" t="s">
         <v>3393</v>
       </c>
@@ -28315,24 +28320,24 @@
         <v>3426</v>
       </c>
       <c r="I794" s="15" t="s">
+        <v>3427</v>
+      </c>
+    </row>
+    <row r="795" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A795" s="1" t="s">
+        <v>3428</v>
+      </c>
+      <c r="B795" s="2" t="s">
+        <v>3429</v>
+      </c>
+      <c r="D795" s="4" t="s">
+        <v>3430</v>
+      </c>
+      <c r="F795" s="6" t="s">
+        <v>3431</v>
+      </c>
+      <c r="I795" s="15" t="s">
         <v>1157</v>
-      </c>
-    </row>
-    <row r="795" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A795" s="1" t="s">
-        <v>3427</v>
-      </c>
-      <c r="B795" s="2" t="s">
-        <v>3428</v>
-      </c>
-      <c r="D795" s="4" t="s">
-        <v>3429</v>
-      </c>
-      <c r="F795" s="6" t="s">
-        <v>3430</v>
-      </c>
-      <c r="I795" s="15" t="s">
-        <v>3431</v>
       </c>
     </row>
     <row r="796" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28352,7 +28357,7 @@
         <v>3436</v>
       </c>
     </row>
-    <row r="797" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="797" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A797" s="1" t="s">
         <v>3437</v>
       </c>
@@ -28467,49 +28472,49 @@
       <c r="F803" s="6" t="s">
         <v>3470</v>
       </c>
+      <c r="I803" s="15" t="s">
+        <v>3471</v>
+      </c>
     </row>
     <row r="804" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A804" s="1" t="s">
-        <v>3471</v>
+        <v>3472</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>3472</v>
+        <v>3473</v>
       </c>
       <c r="D804" s="4" t="s">
-        <v>3473</v>
+        <v>3474</v>
       </c>
       <c r="F804" s="6" t="s">
-        <v>3474</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="805" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A805" s="1" t="s">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="D805" s="4" t="s">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="F805" s="6" t="s">
-        <v>3478</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="806" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A806" s="1" t="s">
-        <v>3479</v>
+        <v>3480</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="D806" s="4" t="s">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="F806" s="6" t="s">
-        <v>3482</v>
-      </c>
-      <c r="I806" s="15" t="s">
         <v>3483</v>
       </c>
     </row>
@@ -28541,30 +28546,30 @@
         <v>3491</v>
       </c>
       <c r="F808" s="6" t="s">
-        <v>3487</v>
+        <v>3492</v>
       </c>
       <c r="I808" s="15" t="s">
-        <v>3488</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="809" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A809" s="1" t="s">
+        <v>3494</v>
+      </c>
+      <c r="B809" s="2" t="s">
+        <v>3495</v>
+      </c>
+      <c r="D809" s="4" t="s">
+        <v>3496</v>
+      </c>
+      <c r="F809" s="6" t="s">
         <v>3492</v>
       </c>
-      <c r="B809" s="2" t="s">
+      <c r="I809" s="15" t="s">
         <v>3493</v>
       </c>
-      <c r="D809" s="4" t="s">
-        <v>3494</v>
-      </c>
-      <c r="F809" s="6" t="s">
-        <v>3495</v>
-      </c>
-      <c r="I809" s="15" t="s">
-        <v>3496</v>
-      </c>
-    </row>
-    <row r="810" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="810" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A810" s="1" t="s">
         <v>3497</v>
       </c>
@@ -28683,7 +28688,7 @@
         <v>3531</v>
       </c>
     </row>
-    <row r="817" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="817" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A817" s="1" t="s">
         <v>3532</v>
       </c>
@@ -28756,33 +28761,33 @@
         <v>3552</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>1172</v>
+        <v>3553</v>
       </c>
       <c r="D821" s="4" t="s">
-        <v>1173</v>
+        <v>3554</v>
       </c>
       <c r="F821" s="6" t="s">
-        <v>1174</v>
+        <v>3555</v>
       </c>
       <c r="I821" s="15" t="s">
-        <v>1175</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="822" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A822" s="1" t="s">
-        <v>3553</v>
+        <v>3557</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>3554</v>
+        <v>1172</v>
       </c>
       <c r="D822" s="4" t="s">
-        <v>3555</v>
+        <v>1173</v>
       </c>
       <c r="F822" s="6" t="s">
-        <v>3556</v>
+        <v>1174</v>
       </c>
       <c r="I822" s="15" t="s">
-        <v>3557</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="823" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28807,33 +28812,33 @@
         <v>3563</v>
       </c>
       <c r="B824" s="2" t="s">
-        <v>1177</v>
+        <v>3564</v>
       </c>
       <c r="D824" s="4" t="s">
-        <v>1178</v>
+        <v>3565</v>
       </c>
       <c r="F824" s="6" t="s">
-        <v>1179</v>
+        <v>3566</v>
       </c>
       <c r="I824" s="15" t="s">
-        <v>1180</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="825" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A825" s="1" t="s">
-        <v>3564</v>
+        <v>3568</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>3565</v>
+        <v>1177</v>
       </c>
       <c r="D825" s="4" t="s">
-        <v>3566</v>
+        <v>1178</v>
       </c>
       <c r="F825" s="6" t="s">
-        <v>3567</v>
+        <v>1179</v>
       </c>
       <c r="I825" s="15" t="s">
-        <v>3568</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="826" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28858,33 +28863,33 @@
         <v>3574</v>
       </c>
       <c r="B827" s="2" t="s">
-        <v>1182</v>
+        <v>3575</v>
       </c>
       <c r="D827" s="4" t="s">
-        <v>1183</v>
+        <v>3576</v>
       </c>
       <c r="F827" s="6" t="s">
-        <v>1184</v>
+        <v>3577</v>
       </c>
       <c r="I827" s="15" t="s">
-        <v>1185</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="828" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A828" s="1" t="s">
-        <v>3575</v>
+        <v>3579</v>
       </c>
       <c r="B828" s="2" t="s">
-        <v>3576</v>
+        <v>1182</v>
       </c>
       <c r="D828" s="4" t="s">
-        <v>3577</v>
+        <v>1183</v>
       </c>
       <c r="F828" s="6" t="s">
-        <v>3578</v>
+        <v>1184</v>
       </c>
       <c r="I828" s="15" t="s">
-        <v>3579</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="829" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28909,33 +28914,33 @@
         <v>3585</v>
       </c>
       <c r="B830" s="2" t="s">
-        <v>1187</v>
+        <v>3586</v>
       </c>
       <c r="D830" s="4" t="s">
-        <v>1188</v>
+        <v>3587</v>
       </c>
       <c r="F830" s="6" t="s">
-        <v>1189</v>
+        <v>3588</v>
       </c>
       <c r="I830" s="15" t="s">
-        <v>1190</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="831" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A831" s="1" t="s">
-        <v>3586</v>
+        <v>3590</v>
       </c>
       <c r="B831" s="2" t="s">
-        <v>3587</v>
+        <v>1187</v>
       </c>
       <c r="D831" s="4" t="s">
-        <v>3588</v>
+        <v>1188</v>
       </c>
       <c r="F831" s="6" t="s">
-        <v>3589</v>
+        <v>1189</v>
       </c>
       <c r="I831" s="15" t="s">
-        <v>3590</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="832" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29087,90 +29092,90 @@
       <c r="F840" s="6" t="s">
         <v>3634</v>
       </c>
+      <c r="I840" s="15" t="s">
+        <v>3635</v>
+      </c>
     </row>
     <row r="841" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A841" s="1" t="s">
-        <v>3635</v>
+        <v>3636</v>
       </c>
       <c r="B841" s="2" t="s">
-        <v>1202</v>
+        <v>3637</v>
+      </c>
+      <c r="D841" s="4" t="s">
+        <v>3638</v>
+      </c>
+      <c r="F841" s="6" t="s">
+        <v>3639</v>
       </c>
     </row>
     <row r="842" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A842" s="1" t="s">
-        <v>3636</v>
+        <v>3640</v>
       </c>
       <c r="B842" s="2" t="s">
-        <v>3637</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="843" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A843" s="1" t="s">
-        <v>3638</v>
+        <v>3641</v>
       </c>
       <c r="B843" s="2" t="s">
-        <v>3639</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="844" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A844" s="1" t="s">
-        <v>3640</v>
+        <v>3643</v>
       </c>
       <c r="B844" s="2" t="s">
-        <v>1209</v>
-      </c>
-      <c r="D844" s="4" t="s">
-        <v>1210</v>
-      </c>
-      <c r="F844" s="6" t="s">
-        <v>1211</v>
-      </c>
-      <c r="I844" s="15" t="s">
-        <v>1212</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="845" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A845" s="1" t="s">
-        <v>3641</v>
+        <v>3645</v>
       </c>
       <c r="B845" s="2" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="D845" s="4" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="F845" s="6" t="s">
-        <v>3642</v>
+        <v>1211</v>
       </c>
       <c r="I845" s="15" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="846" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A846" s="1" t="s">
-        <v>3643</v>
+        <v>3646</v>
       </c>
       <c r="B846" s="2" t="s">
-        <v>3644</v>
+        <v>1214</v>
       </c>
       <c r="D846" s="4" t="s">
-        <v>3645</v>
+        <v>1215</v>
+      </c>
+      <c r="F846" s="6" t="s">
+        <v>3647</v>
+      </c>
+      <c r="I846" s="15" t="s">
+        <v>1217</v>
       </c>
     </row>
     <row r="847" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A847" s="1" t="s">
-        <v>3646</v>
+        <v>3648</v>
       </c>
       <c r="B847" s="2" t="s">
-        <v>3647</v>
+        <v>3649</v>
       </c>
       <c r="D847" s="4" t="s">
-        <v>3648</v>
-      </c>
-      <c r="F847" s="6" t="s">
-        <v>3649</v>
-      </c>
-      <c r="I847" s="15" t="s">
         <v>3650</v>
       </c>
     </row>
@@ -29208,26 +29213,26 @@
         <v>3660</v>
       </c>
     </row>
-    <row r="850" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="850" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A850" s="1" t="s">
         <v>3661</v>
       </c>
       <c r="B850" s="2" t="s">
-        <v>2350</v>
+        <v>3662</v>
       </c>
       <c r="D850" s="4" t="s">
-        <v>2351</v>
+        <v>3663</v>
       </c>
       <c r="F850" s="6" t="s">
-        <v>2352</v>
+        <v>3664</v>
       </c>
       <c r="I850" s="15" t="s">
-        <v>2353</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="851" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A851" s="1" t="s">
-        <v>3662</v>
+        <v>3666</v>
       </c>
       <c r="B851" s="2" t="s">
         <v>2355</v>
@@ -29242,21 +29247,21 @@
         <v>2358</v>
       </c>
     </row>
-    <row r="852" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="852" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A852" s="1" t="s">
-        <v>3663</v>
+        <v>3667</v>
       </c>
       <c r="B852" s="2" t="s">
-        <v>3664</v>
+        <v>2360</v>
       </c>
       <c r="D852" s="4" t="s">
-        <v>3665</v>
+        <v>2361</v>
       </c>
       <c r="F852" s="6" t="s">
-        <v>3666</v>
+        <v>2362</v>
       </c>
       <c r="I852" s="15" t="s">
-        <v>3667</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="853" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29270,24 +29275,24 @@
         <v>3670</v>
       </c>
       <c r="F853" s="6" t="s">
-        <v>3669</v>
+        <v>3671</v>
       </c>
       <c r="I853" s="15" t="s">
-        <v>3671</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="854" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A854" s="1" t="s">
-        <v>3672</v>
+        <v>3673</v>
       </c>
       <c r="B854" s="2" t="s">
-        <v>3673</v>
+        <v>3674</v>
       </c>
       <c r="D854" s="4" t="s">
+        <v>3675</v>
+      </c>
+      <c r="F854" s="6" t="s">
         <v>3674</v>
-      </c>
-      <c r="F854" s="6" t="s">
-        <v>3675</v>
       </c>
       <c r="I854" s="15" t="s">
         <v>3676</v>
@@ -29468,30 +29473,30 @@
         <v>3727</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>1243</v>
+        <v>3728</v>
       </c>
       <c r="D865" s="4" t="s">
-        <v>1244</v>
+        <v>3729</v>
       </c>
       <c r="F865" s="6" t="s">
-        <v>1245</v>
+        <v>3730</v>
       </c>
       <c r="I865" s="15" t="s">
-        <v>3728</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="866" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A866" s="1" t="s">
-        <v>3729</v>
+        <v>3732</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>3730</v>
+        <v>1243</v>
       </c>
       <c r="D866" s="4" t="s">
-        <v>3731</v>
+        <v>1244</v>
       </c>
       <c r="F866" s="6" t="s">
-        <v>3732</v>
+        <v>1245</v>
       </c>
       <c r="I866" s="15" t="s">
         <v>3733</v>
@@ -29596,24 +29601,24 @@
         <v>3762</v>
       </c>
       <c r="I872" s="15" t="s">
-        <v>1251</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="873" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A873" s="1" t="s">
-        <v>3763</v>
+        <v>3764</v>
       </c>
       <c r="B873" s="2" t="s">
-        <v>3764</v>
+        <v>3765</v>
       </c>
       <c r="D873" s="4" t="s">
-        <v>3765</v>
+        <v>3766</v>
       </c>
       <c r="F873" s="6" t="s">
-        <v>3766</v>
+        <v>3767</v>
       </c>
       <c r="I873" s="15" t="s">
-        <v>3767</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="874" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29643,49 +29648,49 @@
       <c r="D875" s="4" t="s">
         <v>3775</v>
       </c>
+      <c r="F875" s="6" t="s">
+        <v>3776</v>
+      </c>
+      <c r="I875" s="15" t="s">
+        <v>3777</v>
+      </c>
     </row>
     <row r="876" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A876" s="1" t="s">
-        <v>3776</v>
+        <v>3778</v>
       </c>
       <c r="B876" s="2" t="s">
-        <v>3777</v>
+        <v>3779</v>
       </c>
       <c r="D876" s="4" t="s">
-        <v>3778</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="877" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A877" s="1" t="s">
-        <v>3779</v>
+        <v>3781</v>
       </c>
       <c r="B877" s="2" t="s">
-        <v>3780</v>
+        <v>3782</v>
       </c>
       <c r="D877" s="4" t="s">
-        <v>3781</v>
-      </c>
-    </row>
-    <row r="878" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="878" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A878" s="1" t="s">
-        <v>3782</v>
+        <v>3784</v>
       </c>
       <c r="B878" s="2" t="s">
-        <v>2476</v>
+        <v>3785</v>
       </c>
       <c r="D878" s="4" t="s">
-        <v>2477</v>
-      </c>
-      <c r="F878" s="6" t="s">
-        <v>3783</v>
-      </c>
-      <c r="I878" s="15" t="s">
-        <v>2479</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="879" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A879" s="1" t="s">
-        <v>3784</v>
+        <v>3787</v>
       </c>
       <c r="B879" s="2" t="s">
         <v>2481</v>
@@ -29694,7 +29699,7 @@
         <v>2482</v>
       </c>
       <c r="F879" s="6" t="s">
-        <v>3785</v>
+        <v>3788</v>
       </c>
       <c r="I879" s="15" t="s">
         <v>2484</v>
@@ -29702,7 +29707,7 @@
     </row>
     <row r="880" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A880" s="1" t="s">
-        <v>3786</v>
+        <v>3789</v>
       </c>
       <c r="B880" s="2" t="s">
         <v>2486</v>
@@ -29711,7 +29716,7 @@
         <v>2487</v>
       </c>
       <c r="F880" s="6" t="s">
-        <v>3787</v>
+        <v>3790</v>
       </c>
       <c r="I880" s="15" t="s">
         <v>2489</v>
@@ -29719,7 +29724,7 @@
     </row>
     <row r="881" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A881" s="1" t="s">
-        <v>3788</v>
+        <v>3791</v>
       </c>
       <c r="B881" s="2" t="s">
         <v>2491</v>
@@ -29728,7 +29733,7 @@
         <v>2492</v>
       </c>
       <c r="F881" s="6" t="s">
-        <v>2493</v>
+        <v>3792</v>
       </c>
       <c r="I881" s="15" t="s">
         <v>2494</v>
@@ -29736,7 +29741,7 @@
     </row>
     <row r="882" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A882" s="1" t="s">
-        <v>3789</v>
+        <v>3793</v>
       </c>
       <c r="B882" s="2" t="s">
         <v>2496</v>
@@ -29753,7 +29758,7 @@
     </row>
     <row r="883" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A883" s="1" t="s">
-        <v>3790</v>
+        <v>3794</v>
       </c>
       <c r="B883" s="2" t="s">
         <v>2501</v>
@@ -29770,7 +29775,7 @@
     </row>
     <row r="884" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A884" s="1" t="s">
-        <v>3791</v>
+        <v>3795</v>
       </c>
       <c r="B884" s="2" t="s">
         <v>2506</v>
@@ -29787,7 +29792,7 @@
     </row>
     <row r="885" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A885" s="1" t="s">
-        <v>3792</v>
+        <v>3796</v>
       </c>
       <c r="B885" s="2" t="s">
         <v>2511</v>
@@ -29804,7 +29809,7 @@
     </row>
     <row r="886" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A886" s="1" t="s">
-        <v>3793</v>
+        <v>3797</v>
       </c>
       <c r="B886" s="2" t="s">
         <v>2516</v>
@@ -29821,7 +29826,7 @@
     </row>
     <row r="887" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A887" s="1" t="s">
-        <v>3794</v>
+        <v>3798</v>
       </c>
       <c r="B887" s="2" t="s">
         <v>2521</v>
@@ -29838,7 +29843,7 @@
     </row>
     <row r="888" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A888" s="1" t="s">
-        <v>3795</v>
+        <v>3799</v>
       </c>
       <c r="B888" s="2" t="s">
         <v>2526</v>
@@ -29855,7 +29860,7 @@
     </row>
     <row r="889" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A889" s="1" t="s">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="B889" s="2" t="s">
         <v>2531</v>
@@ -29872,10 +29877,10 @@
     </row>
     <row r="890" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A890" s="1" t="s">
-        <v>3797</v>
+        <v>3801</v>
       </c>
       <c r="B890" s="2" t="s">
-        <v>3798</v>
+        <v>2536</v>
       </c>
       <c r="D890" s="4" t="s">
         <v>2537</v>
@@ -29889,10 +29894,10 @@
     </row>
     <row r="891" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A891" s="1" t="s">
-        <v>3799</v>
+        <v>3802</v>
       </c>
       <c r="B891" s="2" t="s">
-        <v>2541</v>
+        <v>3803</v>
       </c>
       <c r="D891" s="4" t="s">
         <v>2542</v>
@@ -29906,7 +29911,7 @@
     </row>
     <row r="892" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A892" s="1" t="s">
-        <v>3800</v>
+        <v>3804</v>
       </c>
       <c r="B892" s="2" t="s">
         <v>2546</v>
@@ -29918,12 +29923,12 @@
         <v>2548</v>
       </c>
       <c r="I892" s="15" t="s">
-        <v>3801</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="893" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A893" s="1" t="s">
-        <v>3802</v>
+        <v>3805</v>
       </c>
       <c r="B893" s="2" t="s">
         <v>2551</v>
@@ -29935,12 +29940,12 @@
         <v>2553</v>
       </c>
       <c r="I893" s="15" t="s">
-        <v>2554</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="894" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A894" s="1" t="s">
-        <v>3803</v>
+        <v>3807</v>
       </c>
       <c r="B894" s="2" t="s">
         <v>2556</v>
@@ -29957,7 +29962,7 @@
     </row>
     <row r="895" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A895" s="1" t="s">
-        <v>3804</v>
+        <v>3808</v>
       </c>
       <c r="B895" s="2" t="s">
         <v>2561</v>
@@ -29969,15 +29974,15 @@
         <v>2563</v>
       </c>
       <c r="I895" s="15" t="s">
-        <v>3805</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="896" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A896" s="1" t="s">
-        <v>3806</v>
+        <v>3809</v>
       </c>
       <c r="B896" s="2" t="s">
-        <v>3807</v>
+        <v>2566</v>
       </c>
       <c r="D896" s="4" t="s">
         <v>2567</v>
@@ -29986,15 +29991,15 @@
         <v>2568</v>
       </c>
       <c r="I896" s="15" t="s">
-        <v>2569</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="897" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A897" s="1" t="s">
-        <v>3808</v>
+        <v>3811</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>2571</v>
+        <v>3812</v>
       </c>
       <c r="D897" s="4" t="s">
         <v>2572</v>
@@ -30008,7 +30013,7 @@
     </row>
     <row r="898" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A898" s="1" t="s">
-        <v>3809</v>
+        <v>3813</v>
       </c>
       <c r="B898" s="2" t="s">
         <v>2576</v>
@@ -30020,15 +30025,15 @@
         <v>2578</v>
       </c>
       <c r="I898" s="15" t="s">
-        <v>3810</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="899" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A899" s="1" t="s">
-        <v>3811</v>
+        <v>3814</v>
       </c>
       <c r="B899" s="2" t="s">
-        <v>3812</v>
+        <v>2581</v>
       </c>
       <c r="D899" s="4" t="s">
         <v>2582</v>
@@ -30037,15 +30042,15 @@
         <v>2583</v>
       </c>
       <c r="I899" s="15" t="s">
-        <v>2584</v>
+        <v>3815</v>
       </c>
     </row>
     <row r="900" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A900" s="1" t="s">
-        <v>3813</v>
+        <v>3816</v>
       </c>
       <c r="B900" s="2" t="s">
-        <v>2586</v>
+        <v>3817</v>
       </c>
       <c r="D900" s="4" t="s">
         <v>2587</v>
@@ -30059,7 +30064,7 @@
     </row>
     <row r="901" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A901" s="1" t="s">
-        <v>3814</v>
+        <v>3818</v>
       </c>
       <c r="B901" s="2" t="s">
         <v>2591</v>
@@ -30071,15 +30076,15 @@
         <v>2593</v>
       </c>
       <c r="I901" s="15" t="s">
-        <v>3815</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="902" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A902" s="1" t="s">
-        <v>3816</v>
+        <v>3819</v>
       </c>
       <c r="B902" s="2" t="s">
-        <v>3817</v>
+        <v>2596</v>
       </c>
       <c r="D902" s="4" t="s">
         <v>2597</v>
@@ -30088,15 +30093,15 @@
         <v>2598</v>
       </c>
       <c r="I902" s="15" t="s">
-        <v>2599</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="903" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A903" s="1" t="s">
-        <v>3818</v>
+        <v>3821</v>
       </c>
       <c r="B903" s="2" t="s">
-        <v>2601</v>
+        <v>3822</v>
       </c>
       <c r="D903" s="4" t="s">
         <v>2602</v>
@@ -30110,7 +30115,7 @@
     </row>
     <row r="904" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A904" s="1" t="s">
-        <v>3819</v>
+        <v>3823</v>
       </c>
       <c r="B904" s="2" t="s">
         <v>2606</v>
@@ -30122,15 +30127,15 @@
         <v>2608</v>
       </c>
       <c r="I904" s="15" t="s">
-        <v>3820</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="905" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A905" s="1" t="s">
-        <v>3821</v>
+        <v>3824</v>
       </c>
       <c r="B905" s="2" t="s">
-        <v>3822</v>
+        <v>2611</v>
       </c>
       <c r="D905" s="4" t="s">
         <v>2612</v>
@@ -30138,16 +30143,16 @@
       <c r="F905" s="6" t="s">
         <v>2613</v>
       </c>
-      <c r="I905" s="7" t="s">
-        <v>2614</v>
+      <c r="I905" s="15" t="s">
+        <v>3825</v>
       </c>
     </row>
     <row r="906" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A906" s="1" t="s">
-        <v>3823</v>
+        <v>3826</v>
       </c>
       <c r="B906" s="2" t="s">
-        <v>2616</v>
+        <v>3827</v>
       </c>
       <c r="D906" s="4" t="s">
         <v>2617</v>
@@ -30161,7 +30166,7 @@
     </row>
     <row r="907" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A907" s="1" t="s">
-        <v>3824</v>
+        <v>3828</v>
       </c>
       <c r="B907" s="2" t="s">
         <v>2621</v>
@@ -30173,45 +30178,45 @@
         <v>2623</v>
       </c>
       <c r="I907" s="7" t="s">
-        <v>3825</v>
-      </c>
-    </row>
-    <row r="908" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="908" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A908" s="1" t="s">
-        <v>3826</v>
+        <v>3829</v>
       </c>
       <c r="B908" s="2" t="s">
-        <v>3827</v>
+        <v>2626</v>
       </c>
       <c r="D908" s="4" t="s">
-        <v>3828</v>
+        <v>2627</v>
+      </c>
+      <c r="F908" s="6" t="s">
+        <v>2628</v>
+      </c>
+      <c r="I908" s="7" t="s">
+        <v>3830</v>
       </c>
     </row>
     <row r="909" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A909" s="1" t="s">
-        <v>3829</v>
+        <v>3831</v>
       </c>
       <c r="B909" s="2" t="s">
-        <v>3830</v>
+        <v>3832</v>
       </c>
       <c r="D909" s="4" t="s">
-        <v>3831</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="910" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A910" s="1" t="s">
-        <v>3832</v>
+        <v>3834</v>
       </c>
       <c r="B910" s="2" t="s">
-        <v>3833</v>
+        <v>3835</v>
       </c>
       <c r="D910" s="4" t="s">
-        <v>3834</v>
-      </c>
-      <c r="F910" s="6" t="s">
-        <v>3835</v>
-      </c>
-      <c r="I910" s="15" t="s">
         <v>3836</v>
       </c>
     </row>
@@ -30266,7 +30271,7 @@
         <v>3851</v>
       </c>
     </row>
-    <row r="914" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="914" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A914" s="1" t="s">
         <v>3852</v>
       </c>
@@ -30317,41 +30322,41 @@
         <v>3866</v>
       </c>
     </row>
-    <row r="917" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="917" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A917" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="B917" s="2" t="s">
-        <v>1300</v>
+        <v>3868</v>
       </c>
       <c r="D917" s="4" t="s">
-        <v>1301</v>
+        <v>3869</v>
       </c>
       <c r="F917" s="6" t="s">
-        <v>1302</v>
+        <v>3870</v>
       </c>
       <c r="I917" s="15" t="s">
-        <v>1303</v>
+        <v>3871</v>
       </c>
     </row>
     <row r="918" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A918" s="1" t="s">
-        <v>3868</v>
+        <v>3872</v>
       </c>
       <c r="B918" s="2" t="s">
-        <v>3869</v>
+        <v>1300</v>
       </c>
       <c r="D918" s="4" t="s">
-        <v>3870</v>
+        <v>1301</v>
       </c>
       <c r="F918" s="6" t="s">
-        <v>3871</v>
+        <v>1302</v>
       </c>
       <c r="I918" s="15" t="s">
-        <v>3872</v>
-      </c>
-    </row>
-    <row r="919" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="919" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A919" s="1" t="s">
         <v>3873</v>
       </c>
@@ -30436,62 +30441,62 @@
         <v>3897</v>
       </c>
     </row>
-    <row r="924" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="924" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A924" s="1" t="s">
         <v>3898</v>
       </c>
       <c r="B924" s="2" t="s">
-        <v>1305</v>
+        <v>3899</v>
       </c>
       <c r="D924" s="4" t="s">
-        <v>1306</v>
+        <v>3900</v>
       </c>
       <c r="F924" s="6" t="s">
-        <v>3899</v>
+        <v>3901</v>
+      </c>
+      <c r="I924" s="15" t="s">
+        <v>3902</v>
       </c>
     </row>
     <row r="925" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A925" s="1" t="s">
-        <v>3900</v>
+        <v>3903</v>
       </c>
       <c r="B925" s="2" t="s">
-        <v>3901</v>
+        <v>1305</v>
       </c>
       <c r="D925" s="4" t="s">
-        <v>3902</v>
+        <v>1306</v>
       </c>
       <c r="F925" s="6" t="s">
-        <v>3903</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="926" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A926" s="1" t="s">
-        <v>3904</v>
+        <v>3905</v>
       </c>
       <c r="B926" s="2" t="s">
-        <v>3905</v>
+        <v>3906</v>
       </c>
       <c r="D926" s="4" t="s">
-        <v>3906</v>
+        <v>3907</v>
       </c>
       <c r="F926" s="6" t="s">
-        <v>3907</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="927" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A927" s="1" t="s">
-        <v>3908</v>
+        <v>3909</v>
       </c>
       <c r="B927" s="2" t="s">
-        <v>3909</v>
+        <v>3910</v>
       </c>
       <c r="D927" s="4" t="s">
-        <v>3910</v>
+        <v>3911</v>
       </c>
       <c r="F927" s="6" t="s">
-        <v>3911</v>
-      </c>
-      <c r="I927" s="15" t="s">
         <v>3912</v>
       </c>
     </row>
@@ -30580,7 +30585,7 @@
         <v>3937</v>
       </c>
     </row>
-    <row r="933" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="933" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A933" s="1" t="s">
         <v>3938</v>
       </c>
@@ -30614,7 +30619,7 @@
         <v>3947</v>
       </c>
     </row>
-    <row r="935" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="935" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A935" s="1" t="s">
         <v>3948</v>
       </c>
@@ -30631,7 +30636,7 @@
         <v>3952</v>
       </c>
     </row>
-    <row r="936" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="936" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A936" s="1" t="s">
         <v>3953</v>
       </c>
@@ -30648,7 +30653,7 @@
         <v>3957</v>
       </c>
     </row>
-    <row r="937" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="937" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A937" s="1" t="s">
         <v>3958</v>
       </c>
@@ -30716,7 +30721,7 @@
         <v>3977</v>
       </c>
     </row>
-    <row r="941" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="941" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A941" s="1" t="s">
         <v>3978</v>
       </c>
@@ -30784,7 +30789,7 @@
         <v>3997</v>
       </c>
     </row>
-    <row r="945" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="945" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A945" s="1" t="s">
         <v>3998</v>
       </c>
@@ -30828,54 +30833,54 @@
       <c r="D947" s="4" t="s">
         <v>4010</v>
       </c>
+      <c r="F947" s="6" t="s">
+        <v>4011</v>
+      </c>
+      <c r="I947" s="15" t="s">
+        <v>4012</v>
+      </c>
     </row>
     <row r="948" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A948" s="1" t="s">
-        <v>4011</v>
+        <v>4013</v>
       </c>
       <c r="B948" s="2" t="s">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="D948" s="4" t="s">
-        <v>4013</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="949" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A949" s="1" t="s">
-        <v>4014</v>
+        <v>4016</v>
       </c>
       <c r="B949" s="2" t="s">
-        <v>4015</v>
+        <v>4017</v>
       </c>
       <c r="D949" s="4" t="s">
-        <v>4016</v>
+        <v>4018</v>
       </c>
     </row>
     <row r="950" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A950" s="1" t="s">
-        <v>4017</v>
+        <v>4019</v>
       </c>
       <c r="B950" s="2" t="s">
-        <v>4018</v>
+        <v>4020</v>
       </c>
       <c r="D950" s="4" t="s">
-        <v>4019</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="951" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A951" s="1" t="s">
-        <v>4020</v>
+        <v>4022</v>
       </c>
       <c r="B951" s="2" t="s">
-        <v>4021</v>
+        <v>4023</v>
       </c>
       <c r="D951" s="4" t="s">
-        <v>4022</v>
-      </c>
-      <c r="F951" s="6" t="s">
-        <v>4023</v>
-      </c>
-      <c r="I951" s="15" t="s">
         <v>4024</v>
       </c>
     </row>
@@ -30974,81 +30979,81 @@
       <c r="D957" s="4" t="s">
         <v>4052</v>
       </c>
+      <c r="F957" s="6" t="s">
+        <v>4053</v>
+      </c>
+      <c r="I957" s="15" t="s">
+        <v>4054</v>
+      </c>
     </row>
     <row r="958" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A958" s="1" t="s">
-        <v>4053</v>
+        <v>4055</v>
       </c>
       <c r="B958" s="2" t="s">
-        <v>4054</v>
+        <v>4056</v>
       </c>
       <c r="D958" s="4" t="s">
-        <v>4055</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="959" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A959" s="1" t="s">
-        <v>4056</v>
+        <v>4058</v>
       </c>
       <c r="B959" s="2" t="s">
-        <v>4057</v>
+        <v>4059</v>
       </c>
       <c r="D959" s="4" t="s">
-        <v>4058</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="960" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A960" s="1" t="s">
-        <v>4059</v>
+        <v>4061</v>
       </c>
       <c r="B960" s="2" t="s">
-        <v>1295</v>
+        <v>4062</v>
       </c>
       <c r="D960" s="4" t="s">
-        <v>1296</v>
-      </c>
-      <c r="F960" s="6" t="s">
-        <v>4060</v>
-      </c>
-      <c r="I960" s="15" t="s">
-        <v>4061</v>
+        <v>4063</v>
       </c>
     </row>
     <row r="961" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A961" s="1" t="s">
-        <v>4062</v>
+        <v>4064</v>
       </c>
       <c r="B961" s="2" t="s">
-        <v>1428</v>
+        <v>1295</v>
       </c>
       <c r="D961" s="4" t="s">
-        <v>1429</v>
+        <v>1296</v>
       </c>
       <c r="F961" s="6" t="s">
-        <v>1430</v>
+        <v>4065</v>
       </c>
       <c r="I961" s="15" t="s">
-        <v>4063</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="962" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A962" s="1" t="s">
-        <v>4064</v>
+        <v>4067</v>
       </c>
       <c r="B962" s="2" t="s">
-        <v>4065</v>
+        <v>1428</v>
       </c>
       <c r="D962" s="4" t="s">
-        <v>4066</v>
+        <v>1429</v>
       </c>
       <c r="F962" s="6" t="s">
-        <v>4067</v>
+        <v>1430</v>
       </c>
       <c r="I962" s="15" t="s">
         <v>4068</v>
       </c>
     </row>
-    <row r="963" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="963" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A963" s="1" t="s">
         <v>4069</v>
       </c>
@@ -31082,38 +31087,38 @@
         <v>4078</v>
       </c>
     </row>
-    <row r="965" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="965" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A965" s="1" t="s">
         <v>4079</v>
       </c>
       <c r="B965" s="2" t="s">
-        <v>1370</v>
+        <v>4080</v>
       </c>
       <c r="D965" s="4" t="s">
-        <v>1371</v>
+        <v>4081</v>
       </c>
       <c r="F965" s="6" t="s">
-        <v>1372</v>
+        <v>4082</v>
       </c>
       <c r="I965" s="15" t="s">
-        <v>1373</v>
+        <v>4083</v>
       </c>
     </row>
     <row r="966" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A966" s="1" t="s">
-        <v>4080</v>
+        <v>4084</v>
       </c>
       <c r="B966" s="2" t="s">
-        <v>4081</v>
+        <v>1370</v>
       </c>
       <c r="D966" s="4" t="s">
-        <v>4082</v>
+        <v>1371</v>
       </c>
       <c r="F966" s="6" t="s">
-        <v>4083</v>
+        <v>1372</v>
       </c>
       <c r="I966" s="15" t="s">
-        <v>4084</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="967" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31138,55 +31143,55 @@
         <v>4090</v>
       </c>
       <c r="B968" s="2" t="s">
-        <v>567</v>
+        <v>4091</v>
       </c>
       <c r="D968" s="4" t="s">
-        <v>568</v>
+        <v>4092</v>
       </c>
       <c r="F968" s="6" t="s">
-        <v>569</v>
+        <v>4093</v>
       </c>
       <c r="I968" s="15" t="s">
-        <v>570</v>
+        <v>4094</v>
       </c>
     </row>
     <row r="969" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A969" s="1" t="s">
-        <v>4091</v>
+        <v>4095</v>
       </c>
       <c r="B969" s="2" t="s">
-        <v>1380</v>
+        <v>567</v>
       </c>
       <c r="D969" s="4" t="s">
-        <v>1381</v>
+        <v>568</v>
       </c>
       <c r="F969" s="6" t="s">
-        <v>1382</v>
+        <v>569</v>
       </c>
       <c r="I969" s="15" t="s">
-        <v>1383</v>
+        <v>570</v>
       </c>
     </row>
     <row r="970" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A970" s="1" t="s">
-        <v>4092</v>
+        <v>4096</v>
       </c>
       <c r="B970" s="2" t="s">
-        <v>2853</v>
+        <v>1380</v>
       </c>
       <c r="D970" s="4" t="s">
-        <v>2854</v>
+        <v>1381</v>
       </c>
       <c r="F970" s="6" t="s">
-        <v>4093</v>
+        <v>1382</v>
       </c>
       <c r="I970" s="15" t="s">
-        <v>4094</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="971" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A971" s="1" t="s">
-        <v>4095</v>
+        <v>4097</v>
       </c>
       <c r="B971" s="2" t="s">
         <v>2858</v>
@@ -31195,21 +31200,21 @@
         <v>2859</v>
       </c>
       <c r="F971" s="6" t="s">
-        <v>4096</v>
+        <v>4098</v>
       </c>
       <c r="I971" s="15" t="s">
-        <v>4097</v>
-      </c>
-    </row>
-    <row r="972" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="972" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A972" s="1" t="s">
-        <v>4098</v>
+        <v>4100</v>
       </c>
       <c r="B972" s="2" t="s">
-        <v>4099</v>
+        <v>2863</v>
       </c>
       <c r="D972" s="4" t="s">
-        <v>4100</v>
+        <v>2864</v>
       </c>
       <c r="F972" s="6" t="s">
         <v>4101</v>
@@ -31218,7 +31223,7 @@
         <v>4102</v>
       </c>
     </row>
-    <row r="973" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="973" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A973" s="1" t="s">
         <v>4103</v>
       </c>
@@ -31231,21 +31236,21 @@
       <c r="F973" s="6" t="s">
         <v>4106</v>
       </c>
-    </row>
-    <row r="974" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I973" s="15" t="s">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="974" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A974" s="1" t="s">
-        <v>4107</v>
+        <v>4108</v>
       </c>
       <c r="B974" s="2" t="s">
-        <v>4108</v>
+        <v>4109</v>
       </c>
       <c r="D974" s="4" t="s">
-        <v>4109</v>
+        <v>4110</v>
       </c>
       <c r="F974" s="6" t="s">
-        <v>4110</v>
-      </c>
-      <c r="I974" s="15" t="s">
         <v>4111</v>
       </c>
     </row>
@@ -31300,7 +31305,7 @@
         <v>4126</v>
       </c>
     </row>
-    <row r="978" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="978" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A978" s="1" t="s">
         <v>4127</v>
       </c>
@@ -31314,24 +31319,24 @@
         <v>4130</v>
       </c>
       <c r="I978" s="15" t="s">
-        <v>1416</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="979" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A979" s="1" t="s">
-        <v>4131</v>
+        <v>4132</v>
       </c>
       <c r="B979" s="2" t="s">
-        <v>4132</v>
+        <v>4133</v>
       </c>
       <c r="D979" s="4" t="s">
-        <v>4133</v>
+        <v>4134</v>
       </c>
       <c r="F979" s="6" t="s">
-        <v>4134</v>
+        <v>4135</v>
       </c>
       <c r="I979" s="15" t="s">
-        <v>4135</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="980" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31368,7 +31373,7 @@
         <v>4145</v>
       </c>
     </row>
-    <row r="982" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="982" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A982" s="1" t="s">
         <v>4146</v>
       </c>
@@ -31402,38 +31407,38 @@
         <v>4155</v>
       </c>
     </row>
-    <row r="984" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="984" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A984" s="1" t="s">
         <v>4156</v>
       </c>
       <c r="B984" s="2" t="s">
-        <v>1433</v>
+        <v>4157</v>
       </c>
       <c r="D984" s="4" t="s">
-        <v>1434</v>
+        <v>4158</v>
       </c>
       <c r="F984" s="6" t="s">
-        <v>4157</v>
+        <v>4159</v>
       </c>
       <c r="I984" s="15" t="s">
-        <v>1436</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="985" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A985" s="1" t="s">
-        <v>4158</v>
+        <v>4161</v>
       </c>
       <c r="B985" s="2" t="s">
-        <v>4159</v>
+        <v>1433</v>
       </c>
       <c r="D985" s="4" t="s">
-        <v>4160</v>
+        <v>1434</v>
       </c>
       <c r="F985" s="6" t="s">
-        <v>4161</v>
+        <v>4162</v>
       </c>
       <c r="I985" s="15" t="s">
-        <v>4162</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="986" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31470,55 +31475,55 @@
         <v>4172</v>
       </c>
     </row>
-    <row r="988" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="988" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A988" s="1" t="s">
         <v>4173</v>
       </c>
       <c r="B988" s="2" t="s">
-        <v>1488</v>
+        <v>4174</v>
       </c>
       <c r="D988" s="4" t="s">
-        <v>1489</v>
+        <v>4175</v>
       </c>
       <c r="F988" s="6" t="s">
-        <v>1490</v>
-      </c>
-      <c r="I988" s="7" t="s">
-        <v>1491</v>
+        <v>4176</v>
+      </c>
+      <c r="I988" s="15" t="s">
+        <v>4177</v>
       </c>
     </row>
     <row r="989" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A989" s="1" t="s">
-        <v>4174</v>
+        <v>4178</v>
       </c>
       <c r="B989" s="2" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="D989" s="4" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="F989" s="6" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="I989" s="7" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="990" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A990" s="1" t="s">
-        <v>4175</v>
+        <v>4179</v>
       </c>
       <c r="B990" s="2" t="s">
-        <v>4176</v>
+        <v>1493</v>
       </c>
       <c r="D990" s="4" t="s">
-        <v>4177</v>
+        <v>1494</v>
       </c>
       <c r="F990" s="6" t="s">
-        <v>4178</v>
+        <v>1495</v>
       </c>
       <c r="I990" s="7" t="s">
-        <v>4179</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="991" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31526,50 +31531,50 @@
         <v>4180</v>
       </c>
       <c r="B991" s="2" t="s">
-        <v>1498</v>
+        <v>4181</v>
       </c>
       <c r="D991" s="4" t="s">
-        <v>1499</v>
+        <v>4182</v>
       </c>
       <c r="F991" s="6" t="s">
-        <v>4181</v>
+        <v>4183</v>
       </c>
       <c r="I991" s="7" t="s">
-        <v>1501</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="992" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A992" s="1" t="s">
-        <v>4182</v>
+        <v>4185</v>
       </c>
       <c r="B992" s="2" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="D992" s="4" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="F992" s="6" t="s">
-        <v>1505</v>
+        <v>4186</v>
       </c>
       <c r="I992" s="7" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="993" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A993" s="1" t="s">
-        <v>4183</v>
+        <v>4187</v>
       </c>
       <c r="B993" s="2" t="s">
-        <v>4184</v>
+        <v>1503</v>
       </c>
       <c r="D993" s="4" t="s">
-        <v>4185</v>
+        <v>1504</v>
       </c>
       <c r="F993" s="6" t="s">
-        <v>4186</v>
+        <v>1505</v>
       </c>
       <c r="I993" s="7" t="s">
-        <v>4187</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="994" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31589,26 +31594,26 @@
         <v>4192</v>
       </c>
     </row>
-    <row r="995" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="995" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A995" s="1" t="s">
         <v>4193</v>
       </c>
       <c r="B995" s="2" t="s">
-        <v>1548</v>
+        <v>4194</v>
       </c>
       <c r="D995" s="4" t="s">
-        <v>1549</v>
+        <v>4195</v>
       </c>
       <c r="F995" s="6" t="s">
-        <v>4194</v>
-      </c>
-      <c r="I995" s="15" t="s">
-        <v>4195</v>
+        <v>4196</v>
+      </c>
+      <c r="I995" s="7" t="s">
+        <v>4197</v>
       </c>
     </row>
     <row r="996" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A996" s="1" t="s">
-        <v>4196</v>
+        <v>4198</v>
       </c>
       <c r="B996" s="2" t="s">
         <v>1548</v>
@@ -31617,43 +31622,43 @@
         <v>1549</v>
       </c>
       <c r="F996" s="6" t="s">
-        <v>4197</v>
+        <v>4199</v>
       </c>
       <c r="I996" s="15" t="s">
-        <v>4195</v>
-      </c>
-    </row>
-    <row r="997" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="997" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A997" s="1" t="s">
-        <v>4198</v>
+        <v>4201</v>
       </c>
       <c r="B997" s="2" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="D997" s="4" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
       <c r="F997" s="6" t="s">
-        <v>1555</v>
+        <v>4202</v>
       </c>
       <c r="I997" s="15" t="s">
-        <v>4199</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="998" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A998" s="1" t="s">
-        <v>4200</v>
+        <v>4203</v>
       </c>
       <c r="B998" s="2" t="s">
-        <v>4201</v>
+        <v>1553</v>
       </c>
       <c r="D998" s="4" t="s">
-        <v>4202</v>
+        <v>1554</v>
       </c>
       <c r="F998" s="6" t="s">
-        <v>4203</v>
-      </c>
-      <c r="I998" s="7" t="s">
+        <v>1555</v>
+      </c>
+      <c r="I998" s="15" t="s">
         <v>4204</v>
       </c>
     </row>
@@ -31708,7 +31713,7 @@
         <v>4219</v>
       </c>
     </row>
-    <row r="1002" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1002" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1002" s="1" t="s">
         <v>4220</v>
       </c>
@@ -31721,7 +31726,7 @@
       <c r="F1002" s="6" t="s">
         <v>4223</v>
       </c>
-      <c r="I1002" s="15" t="s">
+      <c r="I1002" s="7" t="s">
         <v>4224</v>
       </c>
     </row>
@@ -31810,7 +31815,7 @@
         <v>4249</v>
       </c>
     </row>
-    <row r="1008" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1008" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1008" s="1" t="s">
         <v>4250</v>
       </c>
@@ -31827,32 +31832,32 @@
         <v>4254</v>
       </c>
     </row>
-    <row r="1009" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1009" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1009" s="1" t="s">
         <v>4255</v>
       </c>
       <c r="B1009" s="2" t="s">
-        <v>1513</v>
+        <v>4256</v>
       </c>
       <c r="D1009" s="4" t="s">
-        <v>1514</v>
+        <v>4257</v>
       </c>
       <c r="F1009" s="6" t="s">
-        <v>4256</v>
+        <v>4258</v>
       </c>
       <c r="I1009" s="15" t="s">
-        <v>4257</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="1010" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1010" s="1" t="s">
-        <v>4258</v>
+        <v>4260</v>
       </c>
       <c r="B1010" s="2" t="s">
-        <v>4259</v>
+        <v>1513</v>
       </c>
       <c r="D1010" s="4" t="s">
-        <v>4260</v>
+        <v>1514</v>
       </c>
       <c r="F1010" s="6" t="s">
         <v>4261</v>
@@ -31866,92 +31871,92 @@
         <v>4263</v>
       </c>
       <c r="B1011" s="2" t="s">
-        <v>1518</v>
+        <v>4264</v>
       </c>
       <c r="D1011" s="4" t="s">
-        <v>1519</v>
+        <v>4265</v>
       </c>
       <c r="F1011" s="6" t="s">
-        <v>1520</v>
+        <v>4266</v>
       </c>
       <c r="I1011" s="15" t="s">
-        <v>1521</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="1012" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1012" s="1" t="s">
-        <v>4264</v>
+        <v>4268</v>
       </c>
       <c r="B1012" s="2" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="D1012" s="4" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="F1012" s="6" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="I1012" s="15" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="1013" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1013" s="1" t="s">
-        <v>4265</v>
+        <v>4269</v>
       </c>
       <c r="B1013" s="2" t="s">
-        <v>1533</v>
+        <v>1523</v>
       </c>
       <c r="D1013" s="4" t="s">
-        <v>1534</v>
+        <v>1524</v>
       </c>
       <c r="F1013" s="6" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
       <c r="I1013" s="15" t="s">
-        <v>1536</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1014" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1014" s="1" t="s">
-        <v>4266</v>
+        <v>4270</v>
       </c>
       <c r="B1014" s="2" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="D1014" s="4" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
       <c r="F1014" s="6" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="I1014" s="15" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="1015" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1015" s="1" t="s">
-        <v>4267</v>
+        <v>4271</v>
       </c>
       <c r="B1015" s="2" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="D1015" s="4" t="s">
-        <v>4268</v>
+        <v>1539</v>
       </c>
       <c r="F1015" s="6" t="s">
-        <v>4269</v>
+        <v>1540</v>
       </c>
       <c r="I1015" s="15" t="s">
-        <v>4270</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1016" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1016" s="1" t="s">
-        <v>4271</v>
+        <v>4272</v>
       </c>
       <c r="B1016" s="2" t="s">
-        <v>4272</v>
+        <v>1543</v>
       </c>
       <c r="D1016" s="4" t="s">
         <v>4273</v>
@@ -31997,7 +32002,7 @@
         <v>4285</v>
       </c>
     </row>
-    <row r="1019" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1019" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1019" s="1" t="s">
         <v>4286</v>
       </c>
@@ -32048,7 +32053,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="1022" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1022" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1022" s="1" t="s">
         <v>4301</v>
       </c>
@@ -32065,7 +32070,7 @@
         <v>4305</v>
       </c>
     </row>
-    <row r="1023" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1023" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1023" s="1" t="s">
         <v>4306</v>
       </c>
@@ -32147,27 +32152,27 @@
         <v>4329</v>
       </c>
       <c r="I1027" s="15" t="s">
-        <v>1661</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="1028" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1028" s="1" t="s">
-        <v>4330</v>
+        <v>4331</v>
       </c>
       <c r="B1028" s="2" t="s">
-        <v>4331</v>
+        <v>4332</v>
       </c>
       <c r="D1028" s="4" t="s">
-        <v>4332</v>
+        <v>4333</v>
       </c>
       <c r="F1028" s="6" t="s">
-        <v>4333</v>
+        <v>4334</v>
       </c>
       <c r="I1028" s="15" t="s">
-        <v>4334</v>
-      </c>
-    </row>
-    <row r="1029" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="1029" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1029" s="1" t="s">
         <v>4335</v>
       </c>
@@ -32211,47 +32216,47 @@
       <c r="D1031" s="4" t="s">
         <v>4347</v>
       </c>
+      <c r="F1031" s="6" t="s">
+        <v>4348</v>
+      </c>
+      <c r="I1031" s="15" t="s">
+        <v>4349</v>
+      </c>
     </row>
     <row r="1032" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1032" s="1" t="s">
-        <v>4348</v>
+        <v>4350</v>
       </c>
       <c r="B1032" s="2" t="s">
-        <v>4349</v>
+        <v>4351</v>
       </c>
       <c r="D1032" s="4" t="s">
-        <v>4350</v>
+        <v>4352</v>
       </c>
     </row>
     <row r="1033" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1033" s="1" t="s">
-        <v>4351</v>
+        <v>4353</v>
       </c>
       <c r="B1033" s="2" t="s">
-        <v>4352</v>
+        <v>4354</v>
       </c>
       <c r="D1033" s="4" t="s">
-        <v>4353</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="1034" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1034" s="1" t="s">
-        <v>4354</v>
+        <v>4356</v>
       </c>
       <c r="B1034" s="2" t="s">
-        <v>4355</v>
+        <v>4357</v>
       </c>
       <c r="D1034" s="4" t="s">
-        <v>4356</v>
-      </c>
-      <c r="F1034" s="6" t="s">
-        <v>4357</v>
-      </c>
-      <c r="I1034" s="15" t="s">
         <v>4358</v>
       </c>
     </row>
-    <row r="1035" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1035" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1035" s="1" t="s">
         <v>4359</v>
       </c>
@@ -32285,7 +32290,7 @@
         <v>4368</v>
       </c>
     </row>
-    <row r="1037" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1037" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1037" s="1" t="s">
         <v>4369</v>
       </c>
@@ -32302,7 +32307,7 @@
         <v>4373</v>
       </c>
     </row>
-    <row r="1038" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1038" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1038" s="1" t="s">
         <v>4374</v>
       </c>
@@ -32336,7 +32341,7 @@
         <v>4383</v>
       </c>
     </row>
-    <row r="1040" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1040" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1040" s="1" t="s">
         <v>4384</v>
       </c>
@@ -32364,24 +32369,24 @@
         <v>4391</v>
       </c>
       <c r="F1041" s="6" t="s">
-        <v>4390</v>
+        <v>4392</v>
       </c>
       <c r="I1041" s="15" t="s">
-        <v>4392</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="1042" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1042" s="1" t="s">
-        <v>4393</v>
+        <v>4394</v>
       </c>
       <c r="B1042" s="2" t="s">
-        <v>4394</v>
+        <v>4395</v>
       </c>
       <c r="D1042" s="4" t="s">
+        <v>4396</v>
+      </c>
+      <c r="F1042" s="6" t="s">
         <v>4395</v>
-      </c>
-      <c r="F1042" s="6" t="s">
-        <v>4396</v>
       </c>
       <c r="I1042" s="15" t="s">
         <v>4397</v>
@@ -32551,24 +32556,24 @@
         <v>4445</v>
       </c>
       <c r="F1052" s="6" t="s">
-        <v>4444</v>
+        <v>4446</v>
       </c>
       <c r="I1052" s="15" t="s">
-        <v>4446</v>
+        <v>4447</v>
       </c>
     </row>
     <row r="1053" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1053" s="1" t="s">
-        <v>4447</v>
+        <v>4448</v>
       </c>
       <c r="B1053" s="2" t="s">
-        <v>4448</v>
+        <v>4449</v>
       </c>
       <c r="D1053" s="4" t="s">
+        <v>4450</v>
+      </c>
+      <c r="F1053" s="6" t="s">
         <v>4449</v>
-      </c>
-      <c r="F1053" s="6" t="s">
-        <v>4450</v>
       </c>
       <c r="I1053" s="15" t="s">
         <v>4451</v>
@@ -32621,21 +32626,21 @@
       <c r="F1056" s="6" t="s">
         <v>4465</v>
       </c>
+      <c r="I1056" s="15" t="s">
+        <v>4466</v>
+      </c>
     </row>
     <row r="1057" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1057" s="1" t="s">
-        <v>4466</v>
+        <v>4467</v>
       </c>
       <c r="B1057" s="2" t="s">
-        <v>4467</v>
+        <v>4468</v>
       </c>
       <c r="D1057" s="4" t="s">
-        <v>4468</v>
+        <v>4469</v>
       </c>
       <c r="F1057" s="6" t="s">
-        <v>4469</v>
-      </c>
-      <c r="I1057" s="15" t="s">
         <v>4470</v>
       </c>
     </row>
@@ -32888,24 +32893,24 @@
         <v>4543</v>
       </c>
       <c r="F1072" s="6" t="s">
-        <v>4542</v>
+        <v>4544</v>
       </c>
       <c r="I1072" s="15" t="s">
-        <v>4544</v>
+        <v>4545</v>
       </c>
     </row>
     <row r="1073" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1073" s="1" t="s">
-        <v>4545</v>
+        <v>4546</v>
       </c>
       <c r="B1073" s="2" t="s">
-        <v>4546</v>
+        <v>4547</v>
       </c>
       <c r="D1073" s="4" t="s">
+        <v>4548</v>
+      </c>
+      <c r="F1073" s="6" t="s">
         <v>4547</v>
-      </c>
-      <c r="F1073" s="6" t="s">
-        <v>4548</v>
       </c>
       <c r="I1073" s="15" t="s">
         <v>4549</v>
@@ -33285,10 +33290,27 @@
         <v>4659</v>
       </c>
     </row>
+    <row r="1096" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1096" s="1" t="s">
+        <v>4660</v>
+      </c>
+      <c r="B1096" s="2" t="s">
+        <v>4661</v>
+      </c>
+      <c r="D1096" s="4" t="s">
+        <v>4662</v>
+      </c>
+      <c r="F1096" s="6" t="s">
+        <v>4663</v>
+      </c>
+      <c r="I1096" s="15" t="s">
+        <v>4664</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K1095">
-    <sortState ref="A2:K1095">
-      <sortCondition ref="A2:A1095"/>
+  <autoFilter ref="A1:K1096">
+    <sortState ref="A2:K1096">
+      <sortCondition ref="A2:A1096"/>
     </sortState>
   </autoFilter>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -33317,117 +33339,117 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>4660</v>
+        <v>4665</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>567</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>4661</v>
+        <v>4666</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>4662</v>
+        <v>4667</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1375</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>4663</v>
+        <v>4668</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>4580</v>
+        <v>4585</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4581</v>
+        <v>4586</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>4664</v>
+        <v>4669</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>2313</v>
+        <v>2318</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>4665</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>3631</v>
+        <v>3636</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>3632</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>4666</v>
+        <v>4671</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>4667</v>
+        <v>4672</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>4668</v>
+        <v>4673</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>3853</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>4669</v>
+        <v>4674</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>3858</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>4670</v>
+        <v>4675</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>2652</v>
+        <v>2657</v>
       </c>
       <c r="C12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>4671</v>
+        <v>4676</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>2657</v>
+        <v>2662</v>
       </c>
       <c r="C13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>4672</v>
+        <v>4677</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>2662</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>3651</v>
+        <v>3656</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>3657</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>2339</v>
+        <v>2344</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>2345</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33441,26 +33463,26 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1710</v>
+        <v>1715</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1711</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1713</v>
+        <v>1718</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1714</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1717</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
